--- a/research/traditional_assets/database/data/hong_kong/hong_kong_trucking.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_trucking.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08826933483635638</v>
+        <v>0.0881612654338764</v>
       </c>
       <c r="C2">
-        <v>38.71251386931311</v>
+        <v>38.3874257248854</v>
       </c>
       <c r="D2">
-        <v>38.22351386931311</v>
+        <v>38.28525400783882</v>
       </c>
       <c r="E2">
-        <v>-4.882828295341411</v>
+        <v>-4.496000012387997</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3868282829534141</v>
       </c>
       <c r="G2">
         <v>0.489</v>
@@ -1433,28 +1433,28 @@
         <v>2.823</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01945746263255673</v>
       </c>
       <c r="N2">
-        <v>2.823</v>
+        <v>2.803542537367444</v>
       </c>
       <c r="O2">
-        <v>0.4657950000000001</v>
+        <v>0.4625845186656282</v>
       </c>
       <c r="P2">
-        <v>2.357205</v>
+        <v>2.340958018701815</v>
       </c>
       <c r="Q2">
-        <v>2.508205</v>
+        <v>2.491958018701815</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08826933483635638</v>
+        <v>0.08862753579179435</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.8347883874325213</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>145.0857212633925</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0881612654338764</v>
+        <v>0.08805319603139641</v>
       </c>
       <c r="C3">
-        <v>38.3874257248854</v>
+        <v>38.06253735338923</v>
       </c>
       <c r="D3">
-        <v>38.28525400783882</v>
+        <v>38.34719391929606</v>
       </c>
       <c r="E3">
-        <v>-4.496000012387997</v>
+        <v>-4.109171729434583</v>
       </c>
       <c r="F3">
-        <v>0.3868282829534141</v>
+        <v>0.7736565659068282</v>
       </c>
       <c r="G3">
         <v>0.489</v>
@@ -1515,28 +1515,28 @@
         <v>2.823</v>
       </c>
       <c r="M3">
-        <v>0.01945746263255673</v>
+        <v>0.03891492526511346</v>
       </c>
       <c r="N3">
-        <v>2.803542537367444</v>
+        <v>2.784085074734887</v>
       </c>
       <c r="O3">
-        <v>0.4625845186656282</v>
+        <v>0.4593740373312564</v>
       </c>
       <c r="P3">
-        <v>2.340958018701815</v>
+        <v>2.324711037403631</v>
       </c>
       <c r="Q3">
-        <v>2.491958018701815</v>
+        <v>2.47571103740363</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08862753579179435</v>
+        <v>0.08899304697081267</v>
       </c>
       <c r="T3">
-        <v>0.8347883874325213</v>
+        <v>0.8419128806371881</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>145.0857212633925</v>
+        <v>72.54286063169624</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08805319603139641</v>
+        <v>0.08794512662891643</v>
       </c>
       <c r="C4">
-        <v>38.06253735338923</v>
+        <v>37.73784972600549</v>
       </c>
       <c r="D4">
-        <v>38.34719391929606</v>
+        <v>38.40933457486574</v>
       </c>
       <c r="E4">
-        <v>-4.109171729434583</v>
+        <v>-3.722343446481169</v>
       </c>
       <c r="F4">
-        <v>0.7736565659068282</v>
+        <v>1.160484848860242</v>
       </c>
       <c r="G4">
         <v>0.489</v>
@@ -1597,28 +1597,28 @@
         <v>2.823</v>
       </c>
       <c r="M4">
-        <v>0.03891492526511346</v>
+        <v>0.05837238789767018</v>
       </c>
       <c r="N4">
-        <v>2.784085074734887</v>
+        <v>2.76462761210233</v>
       </c>
       <c r="O4">
-        <v>0.4593740373312564</v>
+        <v>0.4561635559968845</v>
       </c>
       <c r="P4">
-        <v>2.324711037403631</v>
+        <v>2.308464056105445</v>
       </c>
       <c r="Q4">
-        <v>2.47571103740363</v>
+        <v>2.459464056105445</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08899304697081267</v>
+        <v>0.08936609446280044</v>
       </c>
       <c r="T4">
-        <v>0.8419128806371881</v>
+        <v>0.8491842706089615</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.54286063169624</v>
+        <v>48.3619070877975</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08794512662891643</v>
+        <v>0.08783705722643645</v>
       </c>
       <c r="C5">
-        <v>37.73784972600549</v>
+        <v>37.41336382022041</v>
       </c>
       <c r="D5">
-        <v>38.40933457486574</v>
+        <v>38.47167695203407</v>
       </c>
       <c r="E5">
-        <v>-3.722343446481169</v>
+        <v>-3.335515163527754</v>
       </c>
       <c r="F5">
-        <v>1.160484848860242</v>
+        <v>1.547313131813656</v>
       </c>
       <c r="G5">
         <v>0.489</v>
@@ -1679,28 +1679,28 @@
         <v>2.823</v>
       </c>
       <c r="M5">
-        <v>0.05837238789767018</v>
+        <v>0.07782985053022691</v>
       </c>
       <c r="N5">
-        <v>2.76462761210233</v>
+        <v>2.745170149469773</v>
       </c>
       <c r="O5">
-        <v>0.4561635559968845</v>
+        <v>0.4529530746625126</v>
       </c>
       <c r="P5">
-        <v>2.308464056105445</v>
+        <v>2.292217074807261</v>
       </c>
       <c r="Q5">
-        <v>2.459464056105445</v>
+        <v>2.443217074807261</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08936609446280044</v>
+        <v>0.08974691377753796</v>
       </c>
       <c r="T5">
-        <v>0.8491842706089615</v>
+        <v>0.8566071478718135</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.3619070877975</v>
+        <v>36.27143031584812</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08783705722643645</v>
+        <v>0.08772898782395645</v>
       </c>
       <c r="C6">
-        <v>37.41336382022041</v>
+        <v>37.0890806198768</v>
       </c>
       <c r="D6">
-        <v>38.47167695203407</v>
+        <v>38.53422203464388</v>
       </c>
       <c r="E6">
-        <v>-3.335515163527754</v>
+        <v>-2.94868688057434</v>
       </c>
       <c r="F6">
-        <v>1.547313131813656</v>
+        <v>1.934141414767071</v>
       </c>
       <c r="G6">
         <v>0.489</v>
@@ -1761,28 +1761,28 @@
         <v>2.823</v>
       </c>
       <c r="M6">
-        <v>0.07782985053022691</v>
+        <v>0.09728731316278365</v>
       </c>
       <c r="N6">
-        <v>2.745170149469773</v>
+        <v>2.725712686837217</v>
       </c>
       <c r="O6">
-        <v>0.4529530746625126</v>
+        <v>0.4497425933281408</v>
       </c>
       <c r="P6">
-        <v>2.292217074807261</v>
+        <v>2.275970093509076</v>
       </c>
       <c r="Q6">
-        <v>2.443217074807261</v>
+        <v>2.426970093509075</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08974691377753796</v>
+        <v>0.09013575034100679</v>
       </c>
       <c r="T6">
-        <v>0.8566071478718135</v>
+        <v>0.864186296234936</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.27143031584812</v>
+        <v>29.01714425267849</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08772898782395645</v>
+        <v>0.08762091842147646</v>
       </c>
       <c r="C7">
-        <v>37.0890806198768</v>
+        <v>36.76500111522576</v>
       </c>
       <c r="D7">
-        <v>38.53422203464388</v>
+        <v>38.59697081294625</v>
       </c>
       <c r="E7">
-        <v>-2.94868688057434</v>
+        <v>-2.561858597620926</v>
       </c>
       <c r="F7">
-        <v>1.934141414767071</v>
+        <v>2.320969697720485</v>
       </c>
       <c r="G7">
         <v>0.489</v>
@@ -1843,28 +1843,28 @@
         <v>2.823</v>
       </c>
       <c r="M7">
-        <v>0.09728731316278365</v>
+        <v>0.1167447757953404</v>
       </c>
       <c r="N7">
-        <v>2.725712686837217</v>
+        <v>2.70625522420466</v>
       </c>
       <c r="O7">
-        <v>0.4497425933281408</v>
+        <v>0.4465321119937689</v>
       </c>
       <c r="P7">
-        <v>2.275970093509076</v>
+        <v>2.259723112210891</v>
       </c>
       <c r="Q7">
-        <v>2.426970093509075</v>
+        <v>2.410723112210891</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09013575034100679</v>
+        <v>0.0905328600228473</v>
       </c>
       <c r="T7">
-        <v>0.864186296234936</v>
+        <v>0.8719267030738697</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.01714425267849</v>
+        <v>24.18095354389875</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08762091842147646</v>
+        <v>0.08751284901899647</v>
       </c>
       <c r="C8">
-        <v>36.76500111522576</v>
+        <v>36.441126302979</v>
       </c>
       <c r="D8">
-        <v>38.59697081294625</v>
+        <v>38.6599242836529</v>
       </c>
       <c r="E8">
-        <v>-2.561858597620926</v>
+        <v>-2.175030314667513</v>
       </c>
       <c r="F8">
-        <v>2.320969697720484</v>
+        <v>2.707797980673898</v>
       </c>
       <c r="G8">
         <v>0.489</v>
@@ -1925,28 +1925,28 @@
         <v>2.823</v>
       </c>
       <c r="M8">
-        <v>0.1167447757953404</v>
+        <v>0.1362022384278971</v>
       </c>
       <c r="N8">
-        <v>2.70625522420466</v>
+        <v>2.686797761572103</v>
       </c>
       <c r="O8">
-        <v>0.446532111993769</v>
+        <v>0.4433216306593971</v>
       </c>
       <c r="P8">
-        <v>2.259723112210891</v>
+        <v>2.243476130912706</v>
       </c>
       <c r="Q8">
-        <v>2.410723112210891</v>
+        <v>2.394476130912706</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0905328600228473</v>
+        <v>0.09093850969784567</v>
       </c>
       <c r="T8">
-        <v>0.8719267030738697</v>
+        <v>0.8798335702749308</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.18095354389875</v>
+        <v>20.72653160905607</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08751284901899646</v>
+        <v>0.08740477961651648</v>
       </c>
       <c r="C9">
-        <v>36.441126302979</v>
+        <v>36.11745718636157</v>
       </c>
       <c r="D9">
-        <v>38.65992428365291</v>
+        <v>38.72308344998888</v>
       </c>
       <c r="E9">
-        <v>-2.175030314667512</v>
+        <v>-1.788202031714098</v>
       </c>
       <c r="F9">
-        <v>2.707797980673899</v>
+        <v>3.094626263627313</v>
       </c>
       <c r="G9">
         <v>0.489</v>
@@ -2007,28 +2007,28 @@
         <v>2.823</v>
       </c>
       <c r="M9">
-        <v>0.1362022384278971</v>
+        <v>0.1556597010604538</v>
       </c>
       <c r="N9">
-        <v>2.686797761572103</v>
+        <v>2.667340298939547</v>
       </c>
       <c r="O9">
-        <v>0.4433216306593971</v>
+        <v>0.4401111493250252</v>
       </c>
       <c r="P9">
-        <v>2.243476130912706</v>
+        <v>2.227229149614522</v>
       </c>
       <c r="Q9">
-        <v>2.394476130912706</v>
+        <v>2.378229149614521</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09093850969784567</v>
+        <v>0.09135297784403965</v>
       </c>
       <c r="T9">
-        <v>0.879833570274931</v>
+        <v>0.8879123258934065</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.72653160905607</v>
+        <v>18.13571515792406</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08740477961651648</v>
+        <v>0.08729671021403648</v>
       </c>
       <c r="C10">
-        <v>36.11745718636157</v>
+        <v>35.79399477516519</v>
       </c>
       <c r="D10">
-        <v>38.72308344998888</v>
+        <v>38.78644932174592</v>
       </c>
       <c r="E10">
-        <v>-1.788202031714098</v>
+        <v>-1.401373748760684</v>
       </c>
       <c r="F10">
-        <v>3.094626263627313</v>
+        <v>3.481454546580727</v>
       </c>
       <c r="G10">
         <v>0.489</v>
@@ -2089,28 +2089,28 @@
         <v>2.823</v>
       </c>
       <c r="M10">
-        <v>0.1556597010604538</v>
+        <v>0.1751171636930106</v>
       </c>
       <c r="N10">
-        <v>2.667340298939547</v>
+        <v>2.64788283630699</v>
       </c>
       <c r="O10">
-        <v>0.4401111493250252</v>
+        <v>0.4369006679906534</v>
       </c>
       <c r="P10">
-        <v>2.227229149614522</v>
+        <v>2.210982168316336</v>
       </c>
       <c r="Q10">
-        <v>2.378229149614521</v>
+        <v>2.361982168316336</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09135297784403965</v>
+        <v>0.09177655518025987</v>
       </c>
       <c r="T10">
-        <v>0.8879123258934065</v>
+        <v>0.89616863658042</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.13571515792406</v>
+        <v>16.1206356959325</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08729671021403648</v>
+        <v>0.08718864081155651</v>
       </c>
       <c r="C11">
-        <v>35.79399477516519</v>
+        <v>35.47074008580201</v>
       </c>
       <c r="D11">
-        <v>38.78644932174592</v>
+        <v>38.85002291533615</v>
       </c>
       <c r="E11">
-        <v>-1.401373748760684</v>
+        <v>-1.01454546580727</v>
       </c>
       <c r="F11">
-        <v>3.481454546580727</v>
+        <v>3.868282829534141</v>
       </c>
       <c r="G11">
         <v>0.489</v>
@@ -2171,28 +2171,28 @@
         <v>2.823</v>
       </c>
       <c r="M11">
-        <v>0.1751171636930106</v>
+        <v>0.1945746263255673</v>
       </c>
       <c r="N11">
-        <v>2.64788283630699</v>
+        <v>2.628425373674433</v>
       </c>
       <c r="O11">
-        <v>0.4369006679906534</v>
+        <v>0.4336901866562815</v>
       </c>
       <c r="P11">
-        <v>2.210982168316336</v>
+        <v>2.194735187018152</v>
       </c>
       <c r="Q11">
-        <v>2.361982168316336</v>
+        <v>2.345735187018152</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09177655518025987</v>
+        <v>0.0922095453461739</v>
       </c>
       <c r="T11">
-        <v>0.89616863658042</v>
+        <v>0.9046084208382563</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.1206356959325</v>
+        <v>14.50857212633925</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08718864081155651</v>
+        <v>0.0870805714090765</v>
       </c>
       <c r="C12">
-        <v>35.47074008580201</v>
+        <v>35.14769414135906</v>
       </c>
       <c r="D12">
-        <v>38.85002291533615</v>
+        <v>38.91380525384662</v>
       </c>
       <c r="E12">
-        <v>-1.01454546580727</v>
+        <v>-0.6277171828538561</v>
       </c>
       <c r="F12">
-        <v>3.868282829534141</v>
+        <v>4.255111112487555</v>
       </c>
       <c r="G12">
         <v>0.489</v>
@@ -2253,28 +2253,28 @@
         <v>2.823</v>
       </c>
       <c r="M12">
-        <v>0.1945746263255673</v>
+        <v>0.214032088958124</v>
       </c>
       <c r="N12">
-        <v>2.628425373674433</v>
+        <v>2.608967911041876</v>
       </c>
       <c r="O12">
-        <v>0.4336901866562815</v>
+        <v>0.4304797053219097</v>
       </c>
       <c r="P12">
-        <v>2.194735187018152</v>
+        <v>2.178488205719967</v>
       </c>
       <c r="Q12">
-        <v>2.345735187018152</v>
+        <v>2.329488205719966</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0922095453461739</v>
+        <v>0.09265226562817586</v>
       </c>
       <c r="T12">
-        <v>0.9046084208382563</v>
+        <v>0.9132378631693021</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.50857212633925</v>
+        <v>13.18961102394477</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0870805714090765</v>
+        <v>0.08712280200659654</v>
       </c>
       <c r="C13">
-        <v>35.14769414135906</v>
+        <v>34.73591653332745</v>
       </c>
       <c r="D13">
-        <v>38.91380525384662</v>
+        <v>38.88885592876843</v>
       </c>
       <c r="E13">
-        <v>-0.6277171828538561</v>
+        <v>-0.2408888999004422</v>
       </c>
       <c r="F13">
-        <v>4.255111112487555</v>
+        <v>4.641939395440969</v>
       </c>
       <c r="G13">
         <v>0.489</v>
@@ -2335,45 +2335,45 @@
         <v>2.823</v>
       </c>
       <c r="M13">
-        <v>0.214032088958124</v>
+        <v>0.2404524606838422</v>
       </c>
       <c r="N13">
-        <v>2.608967911041876</v>
+        <v>2.582547539316158</v>
       </c>
       <c r="O13">
-        <v>0.4304797053219097</v>
+        <v>0.4261203439871661</v>
       </c>
       <c r="P13">
-        <v>2.178488205719967</v>
+        <v>2.156427195328992</v>
       </c>
       <c r="Q13">
-        <v>2.329488205719966</v>
+        <v>2.307427195328992</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09265226562817586</v>
+        <v>0.09310504773476878</v>
       </c>
       <c r="T13">
-        <v>0.9132378631693021</v>
+        <v>0.9220634291896899</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.165</v>
       </c>
       <c r="W13">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.18961102394477</v>
+        <v>11.74036644071532</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08712280200659654</v>
+        <v>0.08702725760411655</v>
       </c>
       <c r="C14">
-        <v>34.73591653332745</v>
+        <v>34.40558047973476</v>
       </c>
       <c r="D14">
-        <v>38.88885592876843</v>
+        <v>38.94534815812914</v>
       </c>
       <c r="E14">
-        <v>-0.2408888999004422</v>
+        <v>0.1459393830529727</v>
       </c>
       <c r="F14">
-        <v>4.641939395440969</v>
+        <v>5.028767678394384</v>
       </c>
       <c r="G14">
         <v>0.489</v>
@@ -2417,28 +2417,28 @@
         <v>2.823</v>
       </c>
       <c r="M14">
-        <v>0.2404524606838422</v>
+        <v>0.2604901657408291</v>
       </c>
       <c r="N14">
-        <v>2.582547539316158</v>
+        <v>2.562509834259171</v>
       </c>
       <c r="O14">
-        <v>0.4261203439871661</v>
+        <v>0.4228141226527633</v>
       </c>
       <c r="P14">
-        <v>2.156427195328992</v>
+        <v>2.139695711606408</v>
       </c>
       <c r="Q14">
-        <v>2.307427195328992</v>
+        <v>2.290695711606408</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09310504773476878</v>
+        <v>0.09356823862542131</v>
       </c>
       <c r="T14">
-        <v>0.9220634291896899</v>
+        <v>0.931091881785259</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.74036644071532</v>
+        <v>10.83726132989106</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08702725760411655</v>
+        <v>0.08693171320163656</v>
       </c>
       <c r="C15">
-        <v>34.40558047973476</v>
+        <v>34.07540879275147</v>
       </c>
       <c r="D15">
-        <v>38.94534815812914</v>
+        <v>39.00200475409927</v>
       </c>
       <c r="E15">
-        <v>0.1459393830529727</v>
+        <v>0.5327676660063867</v>
       </c>
       <c r="F15">
-        <v>5.028767678394384</v>
+        <v>5.415595961347798</v>
       </c>
       <c r="G15">
         <v>0.489</v>
@@ -2499,28 +2499,28 @@
         <v>2.823</v>
       </c>
       <c r="M15">
-        <v>0.2604901657408291</v>
+        <v>0.2805278707978159</v>
       </c>
       <c r="N15">
-        <v>2.562509834259171</v>
+        <v>2.542472129202185</v>
       </c>
       <c r="O15">
-        <v>0.4228141226527633</v>
+        <v>0.4195079013183605</v>
       </c>
       <c r="P15">
-        <v>2.139695711606408</v>
+        <v>2.122964227883824</v>
       </c>
       <c r="Q15">
-        <v>2.290695711606408</v>
+        <v>2.273964227883824</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09356823862542131</v>
+        <v>0.09404220139725181</v>
       </c>
       <c r="T15">
-        <v>0.931091881785259</v>
+        <v>0.9403302983946787</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.83726132989106</v>
+        <v>10.06317123489884</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08693171320163656</v>
+        <v>0.08704909379915657</v>
       </c>
       <c r="C16">
-        <v>34.07540879275147</v>
+        <v>33.61899843345312</v>
       </c>
       <c r="D16">
-        <v>39.00200475409927</v>
+        <v>38.93242267775434</v>
       </c>
       <c r="E16">
-        <v>0.5327676660063867</v>
+        <v>0.9195959489598016</v>
       </c>
       <c r="F16">
-        <v>5.415595961347798</v>
+        <v>5.802424244301212</v>
       </c>
       <c r="G16">
         <v>0.489</v>
@@ -2581,45 +2581,45 @@
         <v>2.823</v>
       </c>
       <c r="M16">
-        <v>0.2805278707978159</v>
+        <v>0.3104296970701149</v>
       </c>
       <c r="N16">
-        <v>2.542472129202185</v>
+        <v>2.512570302929885</v>
       </c>
       <c r="O16">
-        <v>0.4195079013183605</v>
+        <v>0.4145740999834311</v>
       </c>
       <c r="P16">
-        <v>2.122964227883824</v>
+        <v>2.097996202946455</v>
       </c>
       <c r="Q16">
-        <v>2.273964227883824</v>
+        <v>2.248996202946454</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09404220139725181</v>
+        <v>0.09452731623430186</v>
       </c>
       <c r="T16">
-        <v>0.9403302983946787</v>
+        <v>0.9497860895125554</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.06317123489884</v>
+        <v>9.093846454266219</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08704909379915657</v>
+        <v>0.08696774439667659</v>
       </c>
       <c r="C17">
-        <v>33.61899843345312</v>
+        <v>33.28036684346533</v>
       </c>
       <c r="D17">
-        <v>38.93242267775434</v>
+        <v>38.98061937071996</v>
       </c>
       <c r="E17">
-        <v>0.9195959489598007</v>
+        <v>1.306424231913215</v>
       </c>
       <c r="F17">
-        <v>5.802424244301212</v>
+        <v>6.189252527254625</v>
       </c>
       <c r="G17">
         <v>0.489</v>
@@ -2663,28 +2663,28 @@
         <v>2.823</v>
       </c>
       <c r="M17">
-        <v>0.3104296970701148</v>
+        <v>0.3311250102081225</v>
       </c>
       <c r="N17">
-        <v>2.512570302929886</v>
+        <v>2.491874989791878</v>
       </c>
       <c r="O17">
-        <v>0.4145740999834312</v>
+        <v>0.4111593733156599</v>
       </c>
       <c r="P17">
-        <v>2.097996202946455</v>
+        <v>2.080715616476218</v>
       </c>
       <c r="Q17">
-        <v>2.248996202946454</v>
+        <v>2.231715616476218</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09452731623430186</v>
+        <v>0.09502398142461499</v>
       </c>
       <c r="T17">
-        <v>0.9497860895125554</v>
+        <v>0.9594670185141909</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.09384645426622</v>
+        <v>8.525481050874582</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08696774439667659</v>
+        <v>0.08688639499419659</v>
       </c>
       <c r="C18">
-        <v>33.28036684346533</v>
+        <v>32.94185473232297</v>
       </c>
       <c r="D18">
-        <v>38.98061937071996</v>
+        <v>39.02893554253101</v>
       </c>
       <c r="E18">
-        <v>1.306424231913215</v>
+        <v>1.69325251486663</v>
       </c>
       <c r="F18">
-        <v>6.189252527254625</v>
+        <v>6.57608081020804</v>
       </c>
       <c r="G18">
         <v>0.489</v>
@@ -2745,28 +2745,28 @@
         <v>2.823</v>
       </c>
       <c r="M18">
-        <v>0.3311250102081225</v>
+        <v>0.3518203233461302</v>
       </c>
       <c r="N18">
-        <v>2.491874989791878</v>
+        <v>2.47117967665387</v>
       </c>
       <c r="O18">
-        <v>0.4111593733156599</v>
+        <v>0.4077446466478886</v>
       </c>
       <c r="P18">
-        <v>2.080715616476218</v>
+        <v>2.063435030005981</v>
       </c>
       <c r="Q18">
-        <v>2.231715616476218</v>
+        <v>2.214435030005981</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09502398142461499</v>
+        <v>0.09553261445083927</v>
       </c>
       <c r="T18">
-        <v>0.9594670185141909</v>
+        <v>0.9693812229134562</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.525481050874582</v>
+        <v>8.023982165529016</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08688639499419659</v>
+        <v>0.0869252855917166</v>
       </c>
       <c r="C19">
-        <v>32.94185473232297</v>
+        <v>32.53191306900621</v>
       </c>
       <c r="D19">
-        <v>39.02893554253101</v>
+        <v>39.00582216216767</v>
       </c>
       <c r="E19">
-        <v>1.69325251486663</v>
+        <v>2.080080797820044</v>
       </c>
       <c r="F19">
-        <v>6.57608081020804</v>
+        <v>6.962909093161454</v>
       </c>
       <c r="G19">
         <v>0.489</v>
@@ -2827,45 +2827,45 @@
         <v>2.823</v>
       </c>
       <c r="M19">
-        <v>0.3518203233461302</v>
+        <v>0.378085963758667</v>
       </c>
       <c r="N19">
-        <v>2.47117967665387</v>
+        <v>2.444914036241333</v>
       </c>
       <c r="O19">
-        <v>0.4077446466478886</v>
+        <v>0.40341081597982</v>
       </c>
       <c r="P19">
-        <v>2.063435030005981</v>
+        <v>2.041503220261513</v>
       </c>
       <c r="Q19">
-        <v>2.214435030005981</v>
+        <v>2.192503220261513</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09553261445083927</v>
+        <v>0.09605365316063</v>
       </c>
       <c r="T19">
-        <v>0.9693812229134562</v>
+        <v>0.9795372371761182</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.023982165529016</v>
+        <v>7.466555943880336</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08692528559171661</v>
+        <v>0.08685061618923663</v>
       </c>
       <c r="C20">
-        <v>32.53191306900621</v>
+        <v>32.18948635806466</v>
       </c>
       <c r="D20">
-        <v>39.00582216216766</v>
+        <v>39.05022373417953</v>
       </c>
       <c r="E20">
-        <v>2.080080797820043</v>
+        <v>2.466909080773457</v>
       </c>
       <c r="F20">
-        <v>6.962909093161453</v>
+        <v>7.349737376114867</v>
       </c>
       <c r="G20">
         <v>0.489</v>
@@ -2909,28 +2909,28 @@
         <v>2.823</v>
       </c>
       <c r="M20">
-        <v>0.3780859637586669</v>
+        <v>0.3990907395230373</v>
       </c>
       <c r="N20">
-        <v>2.444914036241333</v>
+        <v>2.423909260476963</v>
       </c>
       <c r="O20">
-        <v>0.40341081597982</v>
+        <v>0.399945027978699</v>
       </c>
       <c r="P20">
-        <v>2.041503220261513</v>
+        <v>2.023964232498264</v>
       </c>
       <c r="Q20">
-        <v>2.192503220261513</v>
+        <v>2.174964232498264</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09605365316063</v>
+        <v>0.09658755702374891</v>
       </c>
       <c r="T20">
-        <v>0.9795372371761182</v>
+        <v>0.9899440172230434</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.466555943880337</v>
+        <v>7.073579315255057</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08685061618923663</v>
+        <v>0.08677594678675662</v>
       </c>
       <c r="C21">
-        <v>32.18948635806466</v>
+        <v>31.84716084977782</v>
       </c>
       <c r="D21">
-        <v>39.05022373417953</v>
+        <v>39.09472650884611</v>
       </c>
       <c r="E21">
-        <v>2.466909080773457</v>
+        <v>2.853737363726871</v>
       </c>
       <c r="F21">
-        <v>7.349737376114867</v>
+        <v>7.736565659068282</v>
       </c>
       <c r="G21">
         <v>0.489</v>
@@ -2991,28 +2991,28 @@
         <v>2.823</v>
       </c>
       <c r="M21">
-        <v>0.3990907395230373</v>
+        <v>0.4200955152874077</v>
       </c>
       <c r="N21">
-        <v>2.423909260476963</v>
+        <v>2.402904484712593</v>
       </c>
       <c r="O21">
-        <v>0.399945027978699</v>
+        <v>0.3964792399775778</v>
       </c>
       <c r="P21">
-        <v>2.023964232498264</v>
+        <v>2.006425244735015</v>
       </c>
       <c r="Q21">
-        <v>2.174964232498264</v>
+        <v>2.157425244735015</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09658755702374891</v>
+        <v>0.09713480848344579</v>
       </c>
       <c r="T21">
-        <v>0.9899440172230434</v>
+        <v>1.000610966771142</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.073579315255057</v>
+        <v>6.719900349492303</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08677594678675662</v>
+        <v>0.08670127738427665</v>
       </c>
       <c r="C22">
-        <v>31.84716084977782</v>
+        <v>31.50493689054092</v>
       </c>
       <c r="D22">
-        <v>39.09472650884611</v>
+        <v>39.13933083256262</v>
       </c>
       <c r="E22">
-        <v>2.853737363726871</v>
+        <v>3.240565646680285</v>
       </c>
       <c r="F22">
-        <v>7.736565659068282</v>
+        <v>8.123393942021696</v>
       </c>
       <c r="G22">
         <v>0.489</v>
@@ -3073,28 +3073,28 @@
         <v>2.823</v>
       </c>
       <c r="M22">
-        <v>0.4200955152874077</v>
+        <v>0.4411002910517781</v>
       </c>
       <c r="N22">
-        <v>2.402904484712593</v>
+        <v>2.381899708948222</v>
       </c>
       <c r="O22">
-        <v>0.3964792399775778</v>
+        <v>0.3930134519764567</v>
       </c>
       <c r="P22">
-        <v>2.006425244735015</v>
+        <v>1.988886256971766</v>
       </c>
       <c r="Q22">
-        <v>2.157425244735015</v>
+        <v>2.139886256971765</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09713480848344579</v>
+        <v>0.09769591441047676</v>
       </c>
       <c r="T22">
-        <v>1.000610966771142</v>
+        <v>1.011547965674888</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.719900349492303</v>
+        <v>6.399905094754574</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08670127738427665</v>
+        <v>0.08681030798179665</v>
       </c>
       <c r="C23">
-        <v>31.50493689054092</v>
+        <v>31.05301250656377</v>
       </c>
       <c r="D23">
-        <v>39.13933083256262</v>
+        <v>39.07423473153889</v>
       </c>
       <c r="E23">
-        <v>3.240565646680285</v>
+        <v>3.627393929633699</v>
       </c>
       <c r="F23">
-        <v>8.123393942021696</v>
+        <v>8.510222224975109</v>
       </c>
       <c r="G23">
         <v>0.489</v>
@@ -3155,45 +3155,45 @@
         <v>2.823</v>
       </c>
       <c r="M23">
-        <v>0.4411002910517781</v>
+        <v>0.4706152890411235</v>
       </c>
       <c r="N23">
-        <v>2.381899708948222</v>
+        <v>2.352384710958877</v>
       </c>
       <c r="O23">
-        <v>0.3930134519764567</v>
+        <v>0.3881434773082147</v>
       </c>
       <c r="P23">
-        <v>1.988886256971766</v>
+        <v>1.964241233650662</v>
       </c>
       <c r="Q23">
-        <v>2.139886256971765</v>
+        <v>2.115241233650662</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09769591441047676</v>
+        <v>0.09827140766897006</v>
       </c>
       <c r="T23">
-        <v>1.011547965674888</v>
+        <v>1.022765400447962</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.165</v>
       </c>
       <c r="W23">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.399905094754574</v>
+        <v>5.998530149226239</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08681030798179665</v>
+        <v>0.08674398857931666</v>
       </c>
       <c r="C24">
-        <v>31.05301250656377</v>
+        <v>30.70575402353378</v>
       </c>
       <c r="D24">
-        <v>39.07423473153889</v>
+        <v>39.11380453146231</v>
       </c>
       <c r="E24">
-        <v>3.627393929633699</v>
+        <v>4.014222212587113</v>
       </c>
       <c r="F24">
-        <v>8.510222224975109</v>
+        <v>8.897050507928524</v>
       </c>
       <c r="G24">
         <v>0.489</v>
@@ -3237,28 +3237,28 @@
         <v>2.823</v>
       </c>
       <c r="M24">
-        <v>0.4706152890411235</v>
+        <v>0.4920068930884474</v>
       </c>
       <c r="N24">
-        <v>2.352384710958877</v>
+        <v>2.330993106911553</v>
       </c>
       <c r="O24">
-        <v>0.3881434773082147</v>
+        <v>0.3846138626404063</v>
       </c>
       <c r="P24">
-        <v>1.964241233650662</v>
+        <v>1.946379244271147</v>
       </c>
       <c r="Q24">
-        <v>2.115241233650662</v>
+        <v>2.097379244271147</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09827140766897006</v>
+        <v>0.09886184880430735</v>
       </c>
       <c r="T24">
-        <v>1.022765400447962</v>
+        <v>1.034274197163193</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.998530149226239</v>
+        <v>5.737724490564228</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08674398857931666</v>
+        <v>0.08667766917683668</v>
       </c>
       <c r="C25">
-        <v>30.70575402353378</v>
+        <v>30.35857576504619</v>
       </c>
       <c r="D25">
-        <v>39.11380453146231</v>
+        <v>39.15345455592813</v>
       </c>
       <c r="E25">
-        <v>4.014222212587113</v>
+        <v>4.401050495540528</v>
       </c>
       <c r="F25">
-        <v>8.897050507928524</v>
+        <v>9.283878790881939</v>
       </c>
       <c r="G25">
         <v>0.489</v>
@@ -3319,28 +3319,28 @@
         <v>2.823</v>
       </c>
       <c r="M25">
-        <v>0.4920068930884474</v>
+        <v>0.5133984971357712</v>
       </c>
       <c r="N25">
-        <v>2.330993106911553</v>
+        <v>2.309601502864229</v>
       </c>
       <c r="O25">
-        <v>0.3846138626404063</v>
+        <v>0.3810842479725978</v>
       </c>
       <c r="P25">
-        <v>1.946379244271147</v>
+        <v>1.928517254891631</v>
       </c>
       <c r="Q25">
-        <v>2.097379244271147</v>
+        <v>2.079517254891631</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09886184880430735</v>
+        <v>0.09946782786425878</v>
       </c>
       <c r="T25">
-        <v>1.034274197163193</v>
+        <v>1.046085856949877</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.737724490564228</v>
+        <v>5.498652636790718</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08667766917683668</v>
+        <v>0.08661134977435668</v>
       </c>
       <c r="C26">
-        <v>30.35857576504619</v>
+        <v>30.01147797532166</v>
       </c>
       <c r="D26">
-        <v>39.15345455592813</v>
+        <v>39.19318504915702</v>
       </c>
       <c r="E26">
-        <v>4.401050495540527</v>
+        <v>4.787878778493941</v>
       </c>
       <c r="F26">
-        <v>9.283878790881937</v>
+        <v>9.670707073835352</v>
       </c>
       <c r="G26">
         <v>0.489</v>
@@ -3401,28 +3401,28 @@
         <v>2.823</v>
       </c>
       <c r="M26">
-        <v>0.5133984971357711</v>
+        <v>0.534790101183095</v>
       </c>
       <c r="N26">
-        <v>2.309601502864229</v>
+        <v>2.288209898816906</v>
       </c>
       <c r="O26">
-        <v>0.3810842479725978</v>
+        <v>0.3775546333047894</v>
       </c>
       <c r="P26">
-        <v>1.928517254891631</v>
+        <v>1.910655265512116</v>
       </c>
       <c r="Q26">
-        <v>2.079517254891631</v>
+        <v>2.061655265512116</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09946782786425878</v>
+        <v>0.1000899663658089</v>
       </c>
       <c r="T26">
-        <v>1.046085856949877</v>
+        <v>1.058212494330873</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.498652636790719</v>
+        <v>5.27870653131909</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08661134977435668</v>
+        <v>0.0865450303718767</v>
       </c>
       <c r="C27">
-        <v>30.01147797532166</v>
+        <v>29.66446089957308</v>
       </c>
       <c r="D27">
-        <v>39.19318504915702</v>
+        <v>39.23299625636185</v>
       </c>
       <c r="E27">
-        <v>4.787878778493941</v>
+        <v>5.174707061447356</v>
       </c>
       <c r="F27">
-        <v>9.670707073835352</v>
+        <v>10.05753535678877</v>
       </c>
       <c r="G27">
         <v>0.489</v>
@@ -3483,28 +3483,28 @@
         <v>2.823</v>
       </c>
       <c r="M27">
-        <v>0.534790101183095</v>
+        <v>0.5561817052304189</v>
       </c>
       <c r="N27">
-        <v>2.288209898816906</v>
+        <v>2.266818294769581</v>
       </c>
       <c r="O27">
-        <v>0.3775546333047894</v>
+        <v>0.374025018636981</v>
       </c>
       <c r="P27">
-        <v>1.910655265512116</v>
+        <v>1.892793276132601</v>
       </c>
       <c r="Q27">
-        <v>2.061655265512116</v>
+        <v>2.0437932761326</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1000899663658089</v>
+        <v>0.100728919421455</v>
       </c>
       <c r="T27">
-        <v>1.058212494330873</v>
+        <v>1.070666878668112</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.27870653131909</v>
+        <v>5.075679357037585</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0865450303718767</v>
+        <v>0.0864787109693967</v>
       </c>
       <c r="C28">
-        <v>29.66446089957308</v>
+        <v>29.31752478401077</v>
       </c>
       <c r="D28">
-        <v>39.23299625636185</v>
+        <v>39.27288842375295</v>
       </c>
       <c r="E28">
-        <v>5.174707061447356</v>
+        <v>5.561535344400771</v>
       </c>
       <c r="F28">
-        <v>10.05753535678877</v>
+        <v>10.44436363974218</v>
       </c>
       <c r="G28">
         <v>0.489</v>
@@ -3565,28 +3565,28 @@
         <v>2.823</v>
       </c>
       <c r="M28">
-        <v>0.5561817052304189</v>
+        <v>0.5775733092777426</v>
       </c>
       <c r="N28">
-        <v>2.266818294769581</v>
+        <v>2.245426690722258</v>
       </c>
       <c r="O28">
-        <v>0.374025018636981</v>
+        <v>0.3704954039691725</v>
       </c>
       <c r="P28">
-        <v>1.892793276132601</v>
+        <v>1.874931286753085</v>
       </c>
       <c r="Q28">
-        <v>2.0437932761326</v>
+        <v>2.025931286753085</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.100728919421455</v>
+        <v>0.1013853780402695</v>
       </c>
       <c r="T28">
-        <v>1.070666878668112</v>
+        <v>1.083462479014591</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.075679357037585</v>
+        <v>4.88769123270286</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0864787109693967</v>
+        <v>0.08641239156691673</v>
       </c>
       <c r="C29">
-        <v>29.31752478401077</v>
+        <v>28.97066987584736</v>
       </c>
       <c r="D29">
-        <v>39.27288842375295</v>
+        <v>39.31286179854295</v>
       </c>
       <c r="E29">
-        <v>5.561535344400771</v>
+        <v>5.948363627354184</v>
       </c>
       <c r="F29">
-        <v>10.44436363974218</v>
+        <v>10.8311919226956</v>
       </c>
       <c r="G29">
         <v>0.489</v>
@@ -3647,28 +3647,28 @@
         <v>2.823</v>
       </c>
       <c r="M29">
-        <v>0.5775733092777426</v>
+        <v>0.5989649133250664</v>
       </c>
       <c r="N29">
-        <v>2.245426690722258</v>
+        <v>2.224035086674934</v>
       </c>
       <c r="O29">
-        <v>0.3704954039691725</v>
+        <v>0.3669657893013641</v>
       </c>
       <c r="P29">
-        <v>1.874931286753085</v>
+        <v>1.85706929737357</v>
       </c>
       <c r="Q29">
-        <v>2.025931286753085</v>
+        <v>2.00806929737357</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1013853780402695</v>
+        <v>0.1020600716207177</v>
       </c>
       <c r="T29">
-        <v>1.083462479014591</v>
+        <v>1.096613512704028</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.88769123270286</v>
+        <v>4.713130831534901</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08641239156691673</v>
+        <v>0.08634607216443674</v>
       </c>
       <c r="C30">
-        <v>28.97066987584736</v>
+        <v>28.62389642330304</v>
       </c>
       <c r="D30">
-        <v>39.31286179854295</v>
+        <v>39.35291662895205</v>
       </c>
       <c r="E30">
-        <v>5.948363627354184</v>
+        <v>6.335191910307599</v>
       </c>
       <c r="F30">
-        <v>10.8311919226956</v>
+        <v>11.21802020564901</v>
       </c>
       <c r="G30">
         <v>0.489</v>
@@ -3729,28 +3729,28 @@
         <v>2.823</v>
       </c>
       <c r="M30">
-        <v>0.5989649133250664</v>
+        <v>0.6203565173723903</v>
       </c>
       <c r="N30">
-        <v>2.224035086674934</v>
+        <v>2.20264348262761</v>
       </c>
       <c r="O30">
-        <v>0.3669657893013641</v>
+        <v>0.3634361746335557</v>
       </c>
       <c r="P30">
-        <v>1.85706929737357</v>
+        <v>1.839207307994054</v>
       </c>
       <c r="Q30">
-        <v>2.00806929737357</v>
+        <v>1.990207307994054</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1020600716207177</v>
+        <v>0.1027537706541363</v>
       </c>
       <c r="T30">
-        <v>1.096613512704028</v>
+        <v>1.110134998046687</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.713130831534901</v>
+        <v>4.550609078723353</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08634607216443674</v>
+        <v>0.08690600276195674</v>
       </c>
       <c r="C31">
-        <v>28.62389642330304</v>
+        <v>27.90143038273514</v>
       </c>
       <c r="D31">
-        <v>39.35291662895205</v>
+        <v>39.01727887133756</v>
       </c>
       <c r="E31">
-        <v>6.335191910307597</v>
+        <v>6.722020193261012</v>
       </c>
       <c r="F31">
-        <v>11.21802020564901</v>
+        <v>11.60484848860242</v>
       </c>
       <c r="G31">
         <v>0.489</v>
@@ -3811,45 +3811,45 @@
         <v>2.823</v>
       </c>
       <c r="M31">
-        <v>0.6203565173723902</v>
+        <v>0.6707602426412201</v>
       </c>
       <c r="N31">
-        <v>2.20264348262761</v>
+        <v>2.15223975735878</v>
       </c>
       <c r="O31">
-        <v>0.3634361746335557</v>
+        <v>0.3551195599641988</v>
       </c>
       <c r="P31">
-        <v>1.839207307994054</v>
+        <v>1.797120197394582</v>
       </c>
       <c r="Q31">
-        <v>1.990207307994054</v>
+        <v>1.948120197394582</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1027537706541363</v>
+        <v>0.1034672896599382</v>
       </c>
       <c r="T31">
-        <v>1.110134998046687</v>
+        <v>1.124042811541995</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.165</v>
       </c>
       <c r="W31">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.550609078723353</v>
+        <v>4.208657312311788</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08690600276195674</v>
+        <v>0.08686055835947676</v>
       </c>
       <c r="C32">
-        <v>27.90143038273514</v>
+        <v>27.54162909650802</v>
       </c>
       <c r="D32">
-        <v>39.01727887133756</v>
+        <v>39.04430586806386</v>
       </c>
       <c r="E32">
-        <v>6.722020193261012</v>
+        <v>7.108848476214425</v>
       </c>
       <c r="F32">
-        <v>11.60484848860242</v>
+        <v>11.99167677155584</v>
       </c>
       <c r="G32">
         <v>0.489</v>
@@ -3893,28 +3893,28 @@
         <v>2.823</v>
       </c>
       <c r="M32">
-        <v>0.6707602426412201</v>
+        <v>0.6931189173959273</v>
       </c>
       <c r="N32">
-        <v>2.15223975735878</v>
+        <v>2.129881082604073</v>
       </c>
       <c r="O32">
-        <v>0.3551195599641988</v>
+        <v>0.3514303786296721</v>
       </c>
       <c r="P32">
-        <v>1.797120197394582</v>
+        <v>1.778450703974401</v>
       </c>
       <c r="Q32">
-        <v>1.948120197394582</v>
+        <v>1.929450703974401</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1034672896599382</v>
+        <v>0.1042014903760533</v>
       </c>
       <c r="T32">
-        <v>1.124042811541995</v>
+        <v>1.138353750066152</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.208657312311788</v>
+        <v>4.072894173204957</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08686055835947676</v>
+        <v>0.08775031395699676</v>
       </c>
       <c r="C33">
-        <v>27.54162909650802</v>
+        <v>26.63235839639686</v>
       </c>
       <c r="D33">
-        <v>39.04430586806386</v>
+        <v>38.52186345090611</v>
       </c>
       <c r="E33">
-        <v>7.108848476214425</v>
+        <v>7.49567675916784</v>
       </c>
       <c r="F33">
-        <v>11.99167677155584</v>
+        <v>12.37850505450925</v>
       </c>
       <c r="G33">
         <v>0.489</v>
@@ -3975,45 +3975,45 @@
         <v>2.823</v>
       </c>
       <c r="M33">
-        <v>0.6931189173959273</v>
+        <v>0.7588023598414171</v>
       </c>
       <c r="N33">
-        <v>2.129881082604073</v>
+        <v>2.064197640158583</v>
       </c>
       <c r="O33">
-        <v>0.3514303786296721</v>
+        <v>0.3405926106261662</v>
       </c>
       <c r="P33">
-        <v>1.778450703974401</v>
+        <v>1.723605029532417</v>
       </c>
       <c r="Q33">
-        <v>1.929450703974401</v>
+        <v>1.874605029532417</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1042014903760533</v>
+        <v>0.1049572852308776</v>
       </c>
       <c r="T33">
-        <v>1.138353750066152</v>
+        <v>1.153085598546902</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.165</v>
       </c>
       <c r="W33">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.072894173204957</v>
+        <v>3.720336347649185</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08775031395699676</v>
+        <v>0.08773409455451678</v>
       </c>
       <c r="C34">
-        <v>26.63235839639686</v>
+        <v>26.25492860333437</v>
       </c>
       <c r="D34">
-        <v>38.52186345090611</v>
+        <v>38.53126194079704</v>
       </c>
       <c r="E34">
-        <v>7.49567675916784</v>
+        <v>7.882505042121255</v>
       </c>
       <c r="F34">
-        <v>12.37850505450925</v>
+        <v>12.76533333746267</v>
       </c>
       <c r="G34">
         <v>0.489</v>
@@ -4057,28 +4057,28 @@
         <v>2.823</v>
       </c>
       <c r="M34">
-        <v>0.7588023598414171</v>
+        <v>0.7825149335864614</v>
       </c>
       <c r="N34">
-        <v>2.064197640158583</v>
+        <v>2.040485066413539</v>
       </c>
       <c r="O34">
-        <v>0.3405926106261662</v>
+        <v>0.3366800359582339</v>
       </c>
       <c r="P34">
-        <v>1.723605029532417</v>
+        <v>1.703805030455305</v>
       </c>
       <c r="Q34">
-        <v>1.874605029532417</v>
+        <v>1.854805030455305</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1049572852308776</v>
+        <v>0.1057356411261444</v>
       </c>
       <c r="T34">
-        <v>1.153085598546902</v>
+        <v>1.168257203698718</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.720336347649185</v>
+        <v>3.607598882568907</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08773409455451678</v>
+        <v>0.08771787515203677</v>
       </c>
       <c r="C35">
-        <v>26.25492860333437</v>
+        <v>25.87750339744191</v>
       </c>
       <c r="D35">
-        <v>38.53126194079704</v>
+        <v>38.54066501785799</v>
       </c>
       <c r="E35">
-        <v>7.882505042121255</v>
+        <v>8.269333325074669</v>
       </c>
       <c r="F35">
-        <v>12.76533333746267</v>
+        <v>13.15216162041608</v>
       </c>
       <c r="G35">
         <v>0.489</v>
@@ -4139,28 +4139,28 @@
         <v>2.823</v>
       </c>
       <c r="M35">
-        <v>0.7825149335864614</v>
+        <v>0.8062275073315057</v>
       </c>
       <c r="N35">
-        <v>2.040485066413539</v>
+        <v>2.016772492668495</v>
       </c>
       <c r="O35">
-        <v>0.3366800359582339</v>
+        <v>0.3327674612903017</v>
       </c>
       <c r="P35">
-        <v>1.703805030455305</v>
+        <v>1.684005031378193</v>
       </c>
       <c r="Q35">
-        <v>1.854805030455305</v>
+        <v>1.835005031378193</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1057356411261444</v>
+        <v>0.1065375835636921</v>
       </c>
       <c r="T35">
-        <v>1.168257203698718</v>
+        <v>1.183888554461196</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.607598882568907</v>
+        <v>3.501493033081586</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08771787515203677</v>
+        <v>0.08851995574955682</v>
       </c>
       <c r="C36">
-        <v>25.87750339744191</v>
+        <v>25.03110754076017</v>
       </c>
       <c r="D36">
-        <v>38.54066501785799</v>
+        <v>38.08109744412967</v>
       </c>
       <c r="E36">
-        <v>8.269333325074669</v>
+        <v>8.656161608028082</v>
       </c>
       <c r="F36">
-        <v>13.15216162041608</v>
+        <v>13.53898990336949</v>
       </c>
       <c r="G36">
         <v>0.489</v>
@@ -4221,45 +4221,45 @@
         <v>2.823</v>
       </c>
       <c r="M36">
-        <v>0.8062275073315057</v>
+        <v>0.8678492528059846</v>
       </c>
       <c r="N36">
-        <v>2.016772492668495</v>
+        <v>1.955150747194016</v>
       </c>
       <c r="O36">
-        <v>0.3327674612903017</v>
+        <v>0.3225998732870126</v>
       </c>
       <c r="P36">
-        <v>1.684005031378193</v>
+        <v>1.632550873907003</v>
       </c>
       <c r="Q36">
-        <v>1.835005031378193</v>
+        <v>1.783550873907003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1065375835636921</v>
+        <v>0.1073642011531643</v>
       </c>
       <c r="T36">
-        <v>1.183888554461196</v>
+        <v>1.20000086986252</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.165</v>
       </c>
       <c r="W36">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.501493033081586</v>
+        <v>3.252869079361997</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08851995574955682</v>
+        <v>0.08852711634707681</v>
       </c>
       <c r="C37">
-        <v>25.03110754076017</v>
+        <v>24.64022580937114</v>
       </c>
       <c r="D37">
-        <v>38.08109744412967</v>
+        <v>38.07704399569405</v>
       </c>
       <c r="E37">
-        <v>8.656161608028082</v>
+        <v>9.042989890981499</v>
       </c>
       <c r="F37">
-        <v>13.53898990336949</v>
+        <v>13.92581818632291</v>
       </c>
       <c r="G37">
         <v>0.489</v>
@@ -4303,28 +4303,28 @@
         <v>2.823</v>
       </c>
       <c r="M37">
-        <v>0.8678492528059846</v>
+        <v>0.8926449457432986</v>
       </c>
       <c r="N37">
-        <v>1.955150747194016</v>
+        <v>1.930355054256702</v>
       </c>
       <c r="O37">
-        <v>0.3225998732870126</v>
+        <v>0.3185085839523558</v>
       </c>
       <c r="P37">
-        <v>1.632550873907003</v>
+        <v>1.611846470304346</v>
       </c>
       <c r="Q37">
-        <v>1.783550873907003</v>
+        <v>1.762846470304346</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1073642011531643</v>
+        <v>0.1082166505423075</v>
       </c>
       <c r="T37">
-        <v>1.20000086986252</v>
+        <v>1.216616695120134</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.252869079361997</v>
+        <v>3.162511604935275</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08852711634707683</v>
+        <v>0.08853427694459683</v>
       </c>
       <c r="C38">
-        <v>24.64022580937113</v>
+        <v>24.24934494080889</v>
       </c>
       <c r="D38">
-        <v>38.07704399569404</v>
+        <v>38.07299141008522</v>
       </c>
       <c r="E38">
-        <v>9.042989890981495</v>
+        <v>9.429818173934912</v>
       </c>
       <c r="F38">
-        <v>13.92581818632291</v>
+        <v>14.31264646927632</v>
       </c>
       <c r="G38">
         <v>0.489</v>
@@ -4385,28 +4385,28 @@
         <v>2.823</v>
       </c>
       <c r="M38">
-        <v>0.8926449457432984</v>
+        <v>0.9174406386806123</v>
       </c>
       <c r="N38">
-        <v>1.930355054256702</v>
+        <v>1.905559361319388</v>
       </c>
       <c r="O38">
-        <v>0.3185085839523558</v>
+        <v>0.314417294617699</v>
       </c>
       <c r="P38">
-        <v>1.611846470304346</v>
+        <v>1.591142066701689</v>
       </c>
       <c r="Q38">
-        <v>1.762846470304346</v>
+        <v>1.742142066701689</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1082166505423075</v>
+        <v>0.1090961618168204</v>
       </c>
       <c r="T38">
-        <v>1.216616695120134</v>
+        <v>1.233760006893864</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.162511604935275</v>
+        <v>3.077038318315403</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08853427694459683</v>
+        <v>0.09101637754211683</v>
       </c>
       <c r="C39">
-        <v>24.24934494080889</v>
+        <v>22.50788157331184</v>
       </c>
       <c r="D39">
-        <v>38.07299141008522</v>
+        <v>36.71835632554158</v>
       </c>
       <c r="E39">
-        <v>9.429818173934912</v>
+        <v>9.816646456888325</v>
       </c>
       <c r="F39">
-        <v>14.31264646927632</v>
+        <v>14.69947475222973</v>
       </c>
       <c r="G39">
         <v>0.489</v>
@@ -4467,45 +4467,45 @@
         <v>2.823</v>
       </c>
       <c r="M39">
-        <v>0.9174406386806123</v>
+        <v>1.056892234685318</v>
       </c>
       <c r="N39">
-        <v>1.905559361319388</v>
+        <v>1.766107765314682</v>
       </c>
       <c r="O39">
-        <v>0.314417294617699</v>
+        <v>0.2914077812769226</v>
       </c>
       <c r="P39">
-        <v>1.591142066701689</v>
+        <v>1.47469998403776</v>
       </c>
       <c r="Q39">
-        <v>1.742142066701689</v>
+        <v>1.62569998403776</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1090961618168204</v>
+        <v>0.1100040444227691</v>
       </c>
       <c r="T39">
-        <v>1.233760006893864</v>
+        <v>1.251456328724811</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.165</v>
       </c>
       <c r="W39">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.077038318315403</v>
+        <v>2.671038642686715</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09101637754211683</v>
+        <v>0.09108866813963687</v>
       </c>
       <c r="C40">
-        <v>22.50788157331184</v>
+        <v>22.08304300080005</v>
       </c>
       <c r="D40">
-        <v>36.71835632554158</v>
+        <v>36.6803460359832</v>
       </c>
       <c r="E40">
-        <v>9.816646456888325</v>
+        <v>10.20347473984174</v>
       </c>
       <c r="F40">
-        <v>14.69947475222973</v>
+        <v>15.08630303518315</v>
       </c>
       <c r="G40">
         <v>0.489</v>
@@ -4549,28 +4549,28 @@
         <v>2.823</v>
       </c>
       <c r="M40">
-        <v>1.056892234685318</v>
+        <v>1.084705188229669</v>
       </c>
       <c r="N40">
-        <v>1.766107765314682</v>
+        <v>1.738294811770332</v>
       </c>
       <c r="O40">
-        <v>0.2914077812769226</v>
+        <v>0.2868186439421048</v>
       </c>
       <c r="P40">
-        <v>1.47469998403776</v>
+        <v>1.451476167828227</v>
       </c>
       <c r="Q40">
-        <v>1.62569998403776</v>
+        <v>1.602476167828227</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1100040444227691</v>
+        <v>0.1109416936715358</v>
       </c>
       <c r="T40">
-        <v>1.251456328724811</v>
+        <v>1.269732857828903</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.671038642686715</v>
+        <v>2.602550472361414</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09108866813963687</v>
+        <v>0.09116095873715686</v>
       </c>
       <c r="C41">
-        <v>22.08304300080005</v>
+        <v>21.65828304226704</v>
       </c>
       <c r="D41">
-        <v>36.6803460359832</v>
+        <v>36.64241436040361</v>
       </c>
       <c r="E41">
-        <v>10.20347473984174</v>
+        <v>10.59030302279515</v>
       </c>
       <c r="F41">
-        <v>15.08630303518315</v>
+        <v>15.47313131813656</v>
       </c>
       <c r="G41">
         <v>0.489</v>
@@ -4631,28 +4631,28 @@
         <v>2.823</v>
       </c>
       <c r="M41">
-        <v>1.084705188229669</v>
+        <v>1.112518141774019</v>
       </c>
       <c r="N41">
-        <v>1.738294811770332</v>
+        <v>1.710481858225981</v>
       </c>
       <c r="O41">
-        <v>0.2868186439421048</v>
+        <v>0.2822295066072869</v>
       </c>
       <c r="P41">
-        <v>1.451476167828227</v>
+        <v>1.428252351618694</v>
       </c>
       <c r="Q41">
-        <v>1.602476167828227</v>
+        <v>1.579252351618694</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1109416936715358</v>
+        <v>0.1119105978952614</v>
       </c>
       <c r="T41">
-        <v>1.269732857828903</v>
+        <v>1.288618604569799</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.602550472361414</v>
+        <v>2.537486710552379</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09116095873715686</v>
+        <v>0.09256841433467687</v>
       </c>
       <c r="C42">
-        <v>21.65828304226704</v>
+        <v>20.54827124087543</v>
       </c>
       <c r="D42">
-        <v>36.64241436040361</v>
+        <v>35.91923084196542</v>
       </c>
       <c r="E42">
-        <v>10.59030302279515</v>
+        <v>10.97713130574857</v>
       </c>
       <c r="F42">
-        <v>15.47313131813656</v>
+        <v>15.85995960108998</v>
       </c>
       <c r="G42">
         <v>0.489</v>
@@ -4713,45 +4713,45 @@
         <v>2.823</v>
       </c>
       <c r="M42">
-        <v>1.112518141774019</v>
+        <v>1.202184937762621</v>
       </c>
       <c r="N42">
-        <v>1.710481858225981</v>
+        <v>1.62081506223738</v>
       </c>
       <c r="O42">
-        <v>0.2822295066072869</v>
+        <v>0.2674344852691677</v>
       </c>
       <c r="P42">
-        <v>1.428252351618694</v>
+        <v>1.353380576968212</v>
       </c>
       <c r="Q42">
-        <v>1.579252351618694</v>
+        <v>1.504380576968212</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1119105978952614</v>
+        <v>0.1129123463299608</v>
       </c>
       <c r="T42">
-        <v>1.288618604569799</v>
+        <v>1.30814454611547</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.165</v>
       </c>
       <c r="W42">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.537486710552379</v>
+        <v>2.348224396534088</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09256841433467687</v>
+        <v>0.09267326993219689</v>
       </c>
       <c r="C43">
-        <v>20.54827124087543</v>
+        <v>20.10870658136718</v>
       </c>
       <c r="D43">
-        <v>35.91923084196542</v>
+        <v>35.86649446541058</v>
       </c>
       <c r="E43">
-        <v>10.97713130574857</v>
+        <v>11.36395958870198</v>
       </c>
       <c r="F43">
-        <v>15.85995960108998</v>
+        <v>16.24678788404339</v>
       </c>
       <c r="G43">
         <v>0.489</v>
@@ -4795,28 +4795,28 @@
         <v>2.823</v>
       </c>
       <c r="M43">
-        <v>1.202184937762621</v>
+        <v>1.231506521610489</v>
       </c>
       <c r="N43">
-        <v>1.62081506223738</v>
+        <v>1.591493478389511</v>
       </c>
       <c r="O43">
-        <v>0.2674344852691677</v>
+        <v>0.2625964239342694</v>
       </c>
       <c r="P43">
-        <v>1.353380576968212</v>
+        <v>1.328897054455242</v>
       </c>
       <c r="Q43">
-        <v>1.504380576968212</v>
+        <v>1.479897054455242</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1129123463299608</v>
+        <v>0.1139486378141326</v>
       </c>
       <c r="T43">
-        <v>1.30814454611547</v>
+        <v>1.328343795990303</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.348224396534088</v>
+        <v>2.292314291854706</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09267326993219688</v>
+        <v>0.09277812552971691</v>
       </c>
       <c r="C44">
-        <v>20.10870658136719</v>
+        <v>19.6692965492328</v>
       </c>
       <c r="D44">
-        <v>35.86649446541058</v>
+        <v>35.81391271622961</v>
       </c>
       <c r="E44">
-        <v>11.36395958870198</v>
+        <v>11.75078787165539</v>
       </c>
       <c r="F44">
-        <v>16.24678788404339</v>
+        <v>16.63361616699681</v>
       </c>
       <c r="G44">
         <v>0.489</v>
@@ -4877,28 +4877,28 @@
         <v>2.823</v>
       </c>
       <c r="M44">
-        <v>1.231506521610489</v>
+        <v>1.260828105458358</v>
       </c>
       <c r="N44">
-        <v>1.591493478389511</v>
+        <v>1.562171894541643</v>
       </c>
       <c r="O44">
-        <v>0.2625964239342694</v>
+        <v>0.257758362599371</v>
       </c>
       <c r="P44">
-        <v>1.328897054455242</v>
+        <v>1.304413531942271</v>
       </c>
       <c r="Q44">
-        <v>1.479897054455242</v>
+        <v>1.455413531942271</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1139486378141326</v>
+        <v>0.1150212904030121</v>
       </c>
       <c r="T44">
-        <v>1.328343795990303</v>
+        <v>1.349251791474779</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.292314291854706</v>
+        <v>2.239004657160411</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09277812552971691</v>
+        <v>0.0928829811272369</v>
       </c>
       <c r="C45">
-        <v>19.6692965492328</v>
+        <v>19.23004046539769</v>
       </c>
       <c r="D45">
-        <v>35.81391271622961</v>
+        <v>35.76148491534791</v>
       </c>
       <c r="E45">
-        <v>11.75078787165539</v>
+        <v>12.13761615460881</v>
       </c>
       <c r="F45">
-        <v>16.63361616699681</v>
+        <v>17.02044444995022</v>
       </c>
       <c r="G45">
         <v>0.489</v>
@@ -4959,28 +4959,28 @@
         <v>2.823</v>
       </c>
       <c r="M45">
-        <v>1.260828105458358</v>
+        <v>1.290149689306227</v>
       </c>
       <c r="N45">
-        <v>1.562171894541643</v>
+        <v>1.532850310693774</v>
       </c>
       <c r="O45">
-        <v>0.257758362599371</v>
+        <v>0.2529203012644727</v>
       </c>
       <c r="P45">
-        <v>1.304413531942271</v>
+        <v>1.279930009429301</v>
       </c>
       <c r="Q45">
-        <v>1.455413531942271</v>
+        <v>1.430930009429301</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1150212904030121</v>
+        <v>0.116132252012923</v>
       </c>
       <c r="T45">
-        <v>1.349251791474779</v>
+        <v>1.3709065010837</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.239004657160411</v>
+        <v>2.188118187679492</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0928829811272369</v>
+        <v>0.09298783672475694</v>
       </c>
       <c r="C46">
-        <v>19.23004046539769</v>
+        <v>18.79093765475774</v>
       </c>
       <c r="D46">
-        <v>35.76148491534791</v>
+        <v>35.70921038766138</v>
       </c>
       <c r="E46">
-        <v>12.13761615460881</v>
+        <v>12.52444443756222</v>
       </c>
       <c r="F46">
-        <v>17.02044444995022</v>
+        <v>17.40727273290364</v>
       </c>
       <c r="G46">
         <v>0.489</v>
@@ -5041,28 +5041,28 @@
         <v>2.823</v>
       </c>
       <c r="M46">
-        <v>1.290149689306227</v>
+        <v>1.319471273154096</v>
       </c>
       <c r="N46">
-        <v>1.532850310693774</v>
+        <v>1.503528726845905</v>
       </c>
       <c r="O46">
-        <v>0.2529203012644727</v>
+        <v>0.2480822399295743</v>
       </c>
       <c r="P46">
-        <v>1.279930009429301</v>
+        <v>1.25544648691633</v>
       </c>
       <c r="Q46">
-        <v>1.430930009429301</v>
+        <v>1.40644648691633</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.116132252012923</v>
+        <v>0.1172836122268308</v>
       </c>
       <c r="T46">
-        <v>1.3709065010837</v>
+        <v>1.393348654678401</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.188118187679492</v>
+        <v>2.139493339064392</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09298783672475694</v>
+        <v>0.09309269232227695</v>
       </c>
       <c r="C47">
-        <v>18.79093765475774</v>
+        <v>18.35198744615051</v>
       </c>
       <c r="D47">
-        <v>35.70921038766138</v>
+        <v>35.65708846200756</v>
       </c>
       <c r="E47">
-        <v>12.52444443756222</v>
+        <v>12.91127272051564</v>
       </c>
       <c r="F47">
-        <v>17.40727273290364</v>
+        <v>17.79410101585705</v>
       </c>
       <c r="G47">
         <v>0.489</v>
@@ -5123,28 +5123,28 @@
         <v>2.823</v>
       </c>
       <c r="M47">
-        <v>1.319471273154096</v>
+        <v>1.348792857001964</v>
       </c>
       <c r="N47">
-        <v>1.503528726845905</v>
+        <v>1.474207142998036</v>
       </c>
       <c r="O47">
-        <v>0.2480822399295743</v>
+        <v>0.2432441785946759</v>
       </c>
       <c r="P47">
-        <v>1.25544648691633</v>
+        <v>1.23096296440336</v>
       </c>
       <c r="Q47">
-        <v>1.40644648691633</v>
+        <v>1.38196296440336</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1172836122268308</v>
+        <v>0.118477615411624</v>
       </c>
       <c r="T47">
-        <v>1.393348654678401</v>
+        <v>1.41662199914698</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.139493339064392</v>
+        <v>2.092982614302122</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09309269232227695</v>
+        <v>0.09319754791979695</v>
       </c>
       <c r="C48">
-        <v>18.35198744615051</v>
+        <v>17.91318917232635</v>
       </c>
       <c r="D48">
-        <v>35.65708846200756</v>
+        <v>35.60511847113682</v>
       </c>
       <c r="E48">
-        <v>12.91127272051564</v>
+        <v>13.29810100346905</v>
       </c>
       <c r="F48">
-        <v>17.79410101585705</v>
+        <v>18.18092929881046</v>
       </c>
       <c r="G48">
         <v>0.489</v>
@@ -5205,28 +5205,28 @@
         <v>2.823</v>
       </c>
       <c r="M48">
-        <v>1.348792857001964</v>
+        <v>1.378114440849833</v>
       </c>
       <c r="N48">
-        <v>1.474207142998036</v>
+        <v>1.444885559150167</v>
       </c>
       <c r="O48">
-        <v>0.2432441785946759</v>
+        <v>0.2384061172597776</v>
       </c>
       <c r="P48">
-        <v>1.23096296440336</v>
+        <v>1.20647944189039</v>
       </c>
       <c r="Q48">
-        <v>1.38196296440336</v>
+        <v>1.35747944189039</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.118477615411624</v>
+        <v>0.1197166753203716</v>
       </c>
       <c r="T48">
-        <v>1.41662199914698</v>
+        <v>1.440773583029466</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.092982614302122</v>
+        <v>2.048451069316971</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09319754791979695</v>
+        <v>0.09330240351731697</v>
       </c>
       <c r="C49">
-        <v>17.91318917232635</v>
+        <v>17.47454216992004</v>
       </c>
       <c r="D49">
-        <v>35.60511847113682</v>
+        <v>35.55329975168392</v>
       </c>
       <c r="E49">
-        <v>13.29810100346905</v>
+        <v>13.68492928642247</v>
       </c>
       <c r="F49">
-        <v>18.18092929881046</v>
+        <v>18.56775758176388</v>
       </c>
       <c r="G49">
         <v>0.489</v>
@@ -5287,28 +5287,28 @@
         <v>2.823</v>
       </c>
       <c r="M49">
-        <v>1.378114440849833</v>
+        <v>1.407436024697702</v>
       </c>
       <c r="N49">
-        <v>1.444885559150167</v>
+        <v>1.415563975302298</v>
       </c>
       <c r="O49">
-        <v>0.2384061172597776</v>
+        <v>0.2335680559248793</v>
       </c>
       <c r="P49">
-        <v>1.20647944189039</v>
+        <v>1.181995919377419</v>
       </c>
       <c r="Q49">
-        <v>1.35747944189039</v>
+        <v>1.332995919377419</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1197166753203716</v>
+        <v>0.1210033913794557</v>
       </c>
       <c r="T49">
-        <v>1.440773583029466</v>
+        <v>1.465854073984357</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.048451069316971</v>
+        <v>2.005775005372867</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09330240351731697</v>
+        <v>0.09921718911483697</v>
       </c>
       <c r="C50">
-        <v>17.47454216992005</v>
+        <v>14.39037334940869</v>
       </c>
       <c r="D50">
-        <v>35.55329975168392</v>
+        <v>32.85595921412598</v>
       </c>
       <c r="E50">
-        <v>13.68492928642246</v>
+        <v>14.07175756937588</v>
       </c>
       <c r="F50">
-        <v>18.56775758176387</v>
+        <v>18.95458586471729</v>
       </c>
       <c r="G50">
         <v>0.489</v>
@@ -5369,45 +5369,45 @@
         <v>2.823</v>
       </c>
       <c r="M50">
-        <v>1.407436024697702</v>
+        <v>1.705912727824556</v>
       </c>
       <c r="N50">
-        <v>1.415563975302299</v>
+        <v>1.117087272175444</v>
       </c>
       <c r="O50">
-        <v>0.2335680559248793</v>
+        <v>0.1843193999089483</v>
       </c>
       <c r="P50">
-        <v>1.181995919377419</v>
+        <v>0.932767872266496</v>
       </c>
       <c r="Q50">
-        <v>1.332995919377419</v>
+        <v>1.083767872266496</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1210033913794557</v>
+        <v>0.1223405668918372</v>
       </c>
       <c r="T50">
-        <v>1.465854073984357</v>
+        <v>1.491918113604145</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.165</v>
       </c>
       <c r="W50">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.005775005372868</v>
+        <v>1.654832603072254</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09921718911483697</v>
+        <v>0.09944061471235699</v>
       </c>
       <c r="C51">
-        <v>14.39037334940869</v>
+        <v>13.90965468474094</v>
       </c>
       <c r="D51">
-        <v>32.85595921412598</v>
+        <v>32.76206883241165</v>
       </c>
       <c r="E51">
-        <v>14.07175756937588</v>
+        <v>14.45858585232929</v>
       </c>
       <c r="F51">
-        <v>18.95458586471729</v>
+        <v>19.3414141476707</v>
       </c>
       <c r="G51">
         <v>0.489</v>
@@ -5451,28 +5451,28 @@
         <v>2.823</v>
       </c>
       <c r="M51">
-        <v>1.705912727824556</v>
+        <v>1.740727273290363</v>
       </c>
       <c r="N51">
-        <v>1.117087272175444</v>
+        <v>1.082272726709637</v>
       </c>
       <c r="O51">
-        <v>0.1843193999089483</v>
+        <v>0.1785749999070901</v>
       </c>
       <c r="P51">
-        <v>0.932767872266496</v>
+        <v>0.9036977268025469</v>
       </c>
       <c r="Q51">
-        <v>1.083767872266496</v>
+        <v>1.054697726802547</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1223405668918372</v>
+        <v>0.123731229424714</v>
       </c>
       <c r="T51">
-        <v>1.491918113604145</v>
+        <v>1.519024714808724</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.654832603072254</v>
+        <v>1.621735951010809</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09944061471235699</v>
+        <v>0.09966404030987699</v>
       </c>
       <c r="C52">
-        <v>13.90965468474094</v>
+        <v>13.42947110013498</v>
       </c>
       <c r="D52">
-        <v>32.76206883241165</v>
+        <v>32.6687135307591</v>
       </c>
       <c r="E52">
-        <v>14.45858585232929</v>
+        <v>14.84541413528271</v>
       </c>
       <c r="F52">
-        <v>19.3414141476707</v>
+        <v>19.72824243062412</v>
       </c>
       <c r="G52">
         <v>0.489</v>
@@ -5533,28 +5533,28 @@
         <v>2.823</v>
       </c>
       <c r="M52">
-        <v>1.740727273290363</v>
+        <v>1.77554181875617</v>
       </c>
       <c r="N52">
-        <v>1.082272726709637</v>
+        <v>1.04745818124383</v>
       </c>
       <c r="O52">
-        <v>0.1785749999070901</v>
+        <v>0.1728305999052319</v>
       </c>
       <c r="P52">
-        <v>0.9036977268025469</v>
+        <v>0.874627581338598</v>
       </c>
       <c r="Q52">
-        <v>1.054697726802547</v>
+        <v>1.025627581338598</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.123731229424714</v>
+        <v>0.1251786536936265</v>
       </c>
       <c r="T52">
-        <v>1.519024714808724</v>
+        <v>1.547237707899205</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.621735951010809</v>
+        <v>1.589937206873343</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09966404030987699</v>
+        <v>0.09988746590739703</v>
       </c>
       <c r="C53">
-        <v>13.42947110013498</v>
+        <v>12.94981803446621</v>
       </c>
       <c r="D53">
-        <v>32.6687135307591</v>
+        <v>32.57588874804375</v>
       </c>
       <c r="E53">
-        <v>14.84541413528271</v>
+        <v>15.23224241823612</v>
       </c>
       <c r="F53">
-        <v>19.72824243062412</v>
+        <v>20.11507071357753</v>
       </c>
       <c r="G53">
         <v>0.489</v>
@@ -5615,28 +5615,28 @@
         <v>2.823</v>
       </c>
       <c r="M53">
-        <v>1.77554181875617</v>
+        <v>1.810356364221978</v>
       </c>
       <c r="N53">
-        <v>1.04745818124383</v>
+        <v>1.012643635778022</v>
       </c>
       <c r="O53">
-        <v>0.1728305999052319</v>
+        <v>0.1670861999033737</v>
       </c>
       <c r="P53">
-        <v>0.874627581338598</v>
+        <v>0.8455574358746487</v>
       </c>
       <c r="Q53">
-        <v>1.025627581338598</v>
+        <v>0.9965574358746487</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1251786536936265</v>
+        <v>0.1266863873070771</v>
       </c>
       <c r="T53">
-        <v>1.547237707899205</v>
+        <v>1.576626242368456</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.589937206873343</v>
+        <v>1.559361491356547</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09988746590739703</v>
+        <v>0.100110891504917</v>
       </c>
       <c r="C54">
-        <v>12.94981803446621</v>
+        <v>12.4706909783031</v>
       </c>
       <c r="D54">
-        <v>32.57588874804375</v>
+        <v>32.48358997483405</v>
       </c>
       <c r="E54">
-        <v>15.23224241823612</v>
+        <v>15.61907070118954</v>
       </c>
       <c r="F54">
-        <v>20.11507071357753</v>
+        <v>20.50189899653095</v>
       </c>
       <c r="G54">
         <v>0.489</v>
@@ -5697,28 +5697,28 @@
         <v>2.823</v>
       </c>
       <c r="M54">
-        <v>1.810356364221978</v>
+        <v>1.845170909687785</v>
       </c>
       <c r="N54">
-        <v>1.012643635778022</v>
+        <v>0.9778290903122153</v>
       </c>
       <c r="O54">
-        <v>0.1670861999033737</v>
+        <v>0.1613417999015155</v>
       </c>
       <c r="P54">
-        <v>0.8455574358746487</v>
+        <v>0.8164872904106998</v>
       </c>
       <c r="Q54">
-        <v>0.9965574358746487</v>
+        <v>0.9674872904106998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1266863873070771</v>
+        <v>0.1282582797976958</v>
       </c>
       <c r="T54">
-        <v>1.576626242368456</v>
+        <v>1.607265352772568</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.559361491356547</v>
+        <v>1.529939576425292</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.100110891504917</v>
+        <v>0.100334317102437</v>
       </c>
       <c r="C55">
-        <v>12.4706909783031</v>
+        <v>11.99208547317678</v>
       </c>
       <c r="D55">
-        <v>32.48358997483405</v>
+        <v>32.39181275266115</v>
       </c>
       <c r="E55">
-        <v>15.61907070118954</v>
+        <v>16.00589898414295</v>
       </c>
       <c r="F55">
-        <v>20.50189899653095</v>
+        <v>20.88872727948436</v>
       </c>
       <c r="G55">
         <v>0.489</v>
@@ -5779,28 +5779,28 @@
         <v>2.823</v>
       </c>
       <c r="M55">
-        <v>1.845170909687785</v>
+        <v>1.879985455153593</v>
       </c>
       <c r="N55">
-        <v>0.9778290903122153</v>
+        <v>0.9430145448464078</v>
       </c>
       <c r="O55">
-        <v>0.1613417999015155</v>
+        <v>0.1555973998996573</v>
       </c>
       <c r="P55">
-        <v>0.8164872904106998</v>
+        <v>0.7874171449467505</v>
       </c>
       <c r="Q55">
-        <v>0.9674872904106998</v>
+        <v>0.9384171449467505</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1282582797976958</v>
+        <v>0.1298985154400805</v>
       </c>
       <c r="T55">
-        <v>1.607265352772568</v>
+        <v>1.639236598411642</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.529939576425292</v>
+        <v>1.501607362047046</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.100334317102437</v>
+        <v>0.1282943636571632</v>
       </c>
       <c r="C56">
-        <v>11.99208547317678</v>
+        <v>3.144090162519927</v>
       </c>
       <c r="D56">
-        <v>32.39181275266115</v>
+        <v>23.9306457249577</v>
       </c>
       <c r="E56">
-        <v>16.00589898414295</v>
+        <v>16.39272726709637</v>
       </c>
       <c r="F56">
-        <v>20.88872727948436</v>
+        <v>21.27555556243778</v>
       </c>
       <c r="G56">
         <v>0.489</v>
@@ -5861,45 +5861,45 @@
         <v>2.823</v>
       </c>
       <c r="M56">
-        <v>1.879985455153593</v>
+        <v>3.123251556565866</v>
       </c>
       <c r="N56">
-        <v>0.9430145448464078</v>
+        <v>-0.3002515565658657</v>
       </c>
       <c r="O56">
-        <v>0.1555973998996573</v>
+        <v>-0.04954150683336784</v>
       </c>
       <c r="P56">
-        <v>0.7874171449467505</v>
+        <v>-0.2507100497324978</v>
       </c>
       <c r="Q56">
-        <v>0.9384171449467505</v>
+        <v>-0.09971004973249784</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1298985154400805</v>
+        <v>0.1324350068742632</v>
       </c>
       <c r="T56">
-        <v>1.639236598411642</v>
+        <v>1.688677537632887</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.165</v>
+        <v>0.1491378429063074</v>
       </c>
       <c r="W56">
-        <v>0.07514999999999999</v>
+        <v>0.1249065646613541</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.501607362047046</v>
+        <v>0.9038657145836809</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1282943636571632</v>
+        <v>0.1293043636571632</v>
       </c>
       <c r="C57">
-        <v>3.144090162519927</v>
+        <v>2.533567941531867</v>
       </c>
       <c r="D57">
-        <v>23.9306457249577</v>
+        <v>23.70695178692306</v>
       </c>
       <c r="E57">
-        <v>16.39272726709637</v>
+        <v>16.77955555004978</v>
       </c>
       <c r="F57">
-        <v>21.27555556243778</v>
+        <v>21.66238384539119</v>
       </c>
       <c r="G57">
         <v>0.489</v>
@@ -5943,37 +5943,37 @@
         <v>2.823</v>
       </c>
       <c r="M57">
-        <v>3.123251556565866</v>
+        <v>3.180037948503427</v>
       </c>
       <c r="N57">
-        <v>-0.3002515565658657</v>
+        <v>-0.3570379485034265</v>
       </c>
       <c r="O57">
-        <v>-0.04954150683336784</v>
+        <v>-0.05891126150306538</v>
       </c>
       <c r="P57">
-        <v>-0.2507100497324978</v>
+        <v>-0.2981266870003612</v>
       </c>
       <c r="Q57">
-        <v>-0.09971004973249784</v>
+        <v>-0.1471266870003612</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1324350068742632</v>
+        <v>0.1344039843032238</v>
       </c>
       <c r="T57">
-        <v>1.688677537632887</v>
+        <v>1.727056572579089</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1491378429063074</v>
+        <v>0.1464746671401233</v>
       </c>
       <c r="W57">
-        <v>0.1249065646613541</v>
+        <v>0.1252975188638299</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9038657145836809</v>
+        <v>0.8877252553946867</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1293043636571632</v>
+        <v>0.1303143636571632</v>
       </c>
       <c r="C58">
-        <v>2.533567941531867</v>
+        <v>1.927188990747961</v>
       </c>
       <c r="D58">
-        <v>23.70695178692306</v>
+        <v>23.48740111909257</v>
       </c>
       <c r="E58">
-        <v>16.77955555004978</v>
+        <v>17.1663838330032</v>
       </c>
       <c r="F58">
-        <v>21.66238384539119</v>
+        <v>22.04921212834461</v>
       </c>
       <c r="G58">
         <v>0.489</v>
@@ -6025,37 +6025,37 @@
         <v>2.823</v>
       </c>
       <c r="M58">
-        <v>3.180037948503427</v>
+        <v>3.236824340440989</v>
       </c>
       <c r="N58">
-        <v>-0.3570379485034265</v>
+        <v>-0.4138243404409883</v>
       </c>
       <c r="O58">
-        <v>-0.05891126150306538</v>
+        <v>-0.06828101617276307</v>
       </c>
       <c r="P58">
-        <v>-0.2981266870003612</v>
+        <v>-0.3455433242682252</v>
       </c>
       <c r="Q58">
-        <v>-0.1471266870003612</v>
+        <v>-0.1945433242682252</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1344039843032238</v>
+        <v>0.1364645420777173</v>
       </c>
       <c r="T58">
-        <v>1.727056572579089</v>
+        <v>1.767220678918137</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1464746671401233</v>
+        <v>0.143904936137665</v>
       </c>
       <c r="W58">
-        <v>0.1252975188638299</v>
+        <v>0.1256747553749908</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8877252553946867</v>
+        <v>0.8721511281070605</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1303143636571632</v>
+        <v>0.1313243636571632</v>
       </c>
       <c r="C59">
-        <v>1.927188990747961</v>
+        <v>1.324839253664312</v>
       </c>
       <c r="D59">
-        <v>23.48740111909257</v>
+        <v>23.27187966496233</v>
       </c>
       <c r="E59">
-        <v>17.1663838330032</v>
+        <v>17.55321211595661</v>
       </c>
       <c r="F59">
-        <v>22.04921212834461</v>
+        <v>22.43604041129802</v>
       </c>
       <c r="G59">
         <v>0.489</v>
@@ -6107,37 +6107,37 @@
         <v>2.823</v>
       </c>
       <c r="M59">
-        <v>3.236824340440989</v>
+        <v>3.29361073237855</v>
       </c>
       <c r="N59">
-        <v>-0.4138243404409883</v>
+        <v>-0.4706107323785491</v>
       </c>
       <c r="O59">
-        <v>-0.06828101617276307</v>
+        <v>-0.07765077084246061</v>
       </c>
       <c r="P59">
-        <v>-0.3455433242682252</v>
+        <v>-0.3929599615360885</v>
       </c>
       <c r="Q59">
-        <v>-0.1945433242682252</v>
+        <v>-0.2419599615360885</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1364645420777173</v>
+        <v>0.1386232216509963</v>
       </c>
       <c r="T59">
-        <v>1.767220678918137</v>
+        <v>1.809297361749522</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.143904936137665</v>
+        <v>0.1414238165490846</v>
       </c>
       <c r="W59">
-        <v>0.1256747553749908</v>
+        <v>0.1260389837305944</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8721511281070605</v>
+        <v>0.8571140396914216</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1313243636571632</v>
+        <v>0.1323343636571632</v>
       </c>
       <c r="C60">
-        <v>1.324839253664315</v>
+        <v>0.7264088220626697</v>
       </c>
       <c r="D60">
-        <v>23.27187966496233</v>
+        <v>23.0602775163141</v>
       </c>
       <c r="E60">
-        <v>17.5532121159566</v>
+        <v>17.94004039891002</v>
       </c>
       <c r="F60">
-        <v>22.43604041129802</v>
+        <v>22.82286869425143</v>
       </c>
       <c r="G60">
         <v>0.489</v>
@@ -6189,37 +6189,37 @@
         <v>2.823</v>
       </c>
       <c r="M60">
-        <v>3.293610732378549</v>
+        <v>3.35039712431611</v>
       </c>
       <c r="N60">
-        <v>-0.4706107323785487</v>
+        <v>-0.52739712431611</v>
       </c>
       <c r="O60">
-        <v>-0.07765077084246054</v>
+        <v>-0.08702052551215815</v>
       </c>
       <c r="P60">
-        <v>-0.3929599615360881</v>
+        <v>-0.4403765988039518</v>
       </c>
       <c r="Q60">
-        <v>-0.2419599615360881</v>
+        <v>-0.2893765988039518</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1386232216509963</v>
+        <v>0.1408872026668743</v>
       </c>
       <c r="T60">
-        <v>1.809297361749521</v>
+        <v>1.853426565694632</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1414238165490846</v>
+        <v>0.1390268027092696</v>
       </c>
       <c r="W60">
-        <v>0.1260389837305944</v>
+        <v>0.1263908653622792</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8571140396914217</v>
+        <v>0.8425866830864823</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1323343636571632</v>
+        <v>0.1333443636571632</v>
       </c>
       <c r="C61">
-        <v>0.7264088220626697</v>
+        <v>0.1317917491160898</v>
       </c>
       <c r="D61">
-        <v>23.0602775163141</v>
+        <v>22.85248872632094</v>
       </c>
       <c r="E61">
-        <v>17.94004039891002</v>
+        <v>18.32686868186343</v>
       </c>
       <c r="F61">
-        <v>22.82286869425143</v>
+        <v>23.20969697720485</v>
       </c>
       <c r="G61">
         <v>0.489</v>
@@ -6271,37 +6271,37 @@
         <v>2.823</v>
       </c>
       <c r="M61">
-        <v>3.35039712431611</v>
+        <v>3.407183516253672</v>
       </c>
       <c r="N61">
-        <v>-0.52739712431611</v>
+        <v>-0.5841835162536713</v>
       </c>
       <c r="O61">
-        <v>-0.08702052551215815</v>
+        <v>-0.09639028018185576</v>
       </c>
       <c r="P61">
-        <v>-0.4403765988039518</v>
+        <v>-0.4877932360718155</v>
       </c>
       <c r="Q61">
-        <v>-0.2893765988039518</v>
+        <v>-0.3367932360718155</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1408872026668743</v>
+        <v>0.1432643827335461</v>
       </c>
       <c r="T61">
-        <v>1.853426565694632</v>
+        <v>1.899762229836997</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1390268027092696</v>
+        <v>0.1367096893307818</v>
       </c>
       <c r="W61">
-        <v>0.1263908653622792</v>
+        <v>0.1267310176062413</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8425866830864823</v>
+        <v>0.8285435717017077</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1333443636571632</v>
+        <v>0.1343543636571632</v>
       </c>
       <c r="C62">
-        <v>0.1317917491160898</v>
+        <v>-0.4591141274914072</v>
       </c>
       <c r="D62">
-        <v>22.85248872632094</v>
+        <v>22.64841113266685</v>
       </c>
       <c r="E62">
-        <v>18.32686868186343</v>
+        <v>18.71369696481685</v>
       </c>
       <c r="F62">
-        <v>23.20969697720485</v>
+        <v>23.59652526015826</v>
       </c>
       <c r="G62">
         <v>0.489</v>
@@ -6353,37 +6353,37 @@
         <v>2.823</v>
       </c>
       <c r="M62">
-        <v>3.407183516253672</v>
+        <v>3.463969908191233</v>
       </c>
       <c r="N62">
-        <v>-0.5841835162536713</v>
+        <v>-0.6409699081912326</v>
       </c>
       <c r="O62">
-        <v>-0.09639028018185576</v>
+        <v>-0.1057600348515534</v>
       </c>
       <c r="P62">
-        <v>-0.4877932360718155</v>
+        <v>-0.5352098733396792</v>
       </c>
       <c r="Q62">
-        <v>-0.3367932360718155</v>
+        <v>-0.3842098733396792</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1432643827335461</v>
+        <v>0.1457634694703037</v>
       </c>
       <c r="T62">
-        <v>1.899762229836997</v>
+        <v>1.9484740818841</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1367096893307818</v>
+        <v>0.1344685468827362</v>
       </c>
       <c r="W62">
-        <v>0.1267310176062413</v>
+        <v>0.1270600173176143</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8285435717017077</v>
+        <v>0.8149608901984009</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1343543636571632</v>
+        <v>0.1353643636571632</v>
       </c>
       <c r="C63">
-        <v>-0.4591141274914072</v>
+        <v>-1.046407353051578</v>
       </c>
       <c r="D63">
-        <v>22.64841113266685</v>
+        <v>22.44794619006009</v>
       </c>
       <c r="E63">
-        <v>18.71369696481685</v>
+        <v>19.10052524777026</v>
       </c>
       <c r="F63">
-        <v>23.59652526015826</v>
+        <v>23.98335354311167</v>
       </c>
       <c r="G63">
         <v>0.489</v>
@@ -6435,37 +6435,37 @@
         <v>2.823</v>
       </c>
       <c r="M63">
-        <v>3.463969908191233</v>
+        <v>3.520756300128794</v>
       </c>
       <c r="N63">
-        <v>-0.6409699081912326</v>
+        <v>-0.6977563001287934</v>
       </c>
       <c r="O63">
-        <v>-0.1057600348515534</v>
+        <v>-0.1151297895212509</v>
       </c>
       <c r="P63">
-        <v>-0.5352098733396792</v>
+        <v>-0.5826265106075426</v>
       </c>
       <c r="Q63">
-        <v>-0.3842098733396792</v>
+        <v>-0.4316265106075425</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1457634694703037</v>
+        <v>0.1483940870879433</v>
       </c>
       <c r="T63">
-        <v>1.9484740818841</v>
+        <v>1.999749715617892</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1344685468827362</v>
+        <v>0.1322996993523695</v>
       </c>
       <c r="W63">
-        <v>0.1270600173176143</v>
+        <v>0.1273784041350722</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8149608901984009</v>
+        <v>0.80181635971133</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1353643636571632</v>
+        <v>0.1713311834485907</v>
       </c>
       <c r="C64">
-        <v>-1.046407353051578</v>
+        <v>-6.81305054038469</v>
       </c>
       <c r="D64">
-        <v>22.44794619006009</v>
+        <v>17.0681312856804</v>
       </c>
       <c r="E64">
-        <v>19.10052524777026</v>
+        <v>19.48735353072368</v>
       </c>
       <c r="F64">
-        <v>23.98335354311167</v>
+        <v>24.37018182606509</v>
       </c>
       <c r="G64">
         <v>0.489</v>
@@ -6517,45 +6517,45 @@
         <v>2.823</v>
       </c>
       <c r="M64">
-        <v>3.520756300128794</v>
+        <v>4.89353251067387</v>
       </c>
       <c r="N64">
-        <v>-0.6977563001287934</v>
+        <v>-2.070532510673869</v>
       </c>
       <c r="O64">
-        <v>-0.1151297895212509</v>
+        <v>-0.3416378642611885</v>
       </c>
       <c r="P64">
-        <v>-0.5826265106075426</v>
+        <v>-1.728894646412681</v>
       </c>
       <c r="Q64">
-        <v>-0.4316265106075425</v>
+        <v>-1.577894646412681</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1483940870879433</v>
+        <v>0.1536988456347189</v>
       </c>
       <c r="T64">
-        <v>1.999749715617892</v>
+        <v>2.103149333436439</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1322996993523695</v>
+        <v>0.09518583946954451</v>
       </c>
       <c r="W64">
-        <v>0.1273784041350722</v>
+        <v>0.1816866834345155</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.80181635971133</v>
+        <v>0.576883875572997</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1713311834485907</v>
+        <v>0.1728811834485907</v>
       </c>
       <c r="C65">
-        <v>-6.81305054038469</v>
+        <v>-7.374358128708572</v>
       </c>
       <c r="D65">
-        <v>17.0681312856804</v>
+        <v>16.89365198030993</v>
       </c>
       <c r="E65">
-        <v>19.48735353072368</v>
+        <v>19.87418181367709</v>
       </c>
       <c r="F65">
-        <v>24.37018182606509</v>
+        <v>24.7570101090185</v>
       </c>
       <c r="G65">
         <v>0.489</v>
@@ -6599,37 +6599,37 @@
         <v>2.823</v>
       </c>
       <c r="M65">
-        <v>4.89353251067387</v>
+        <v>4.971207629890915</v>
       </c>
       <c r="N65">
-        <v>-2.070532510673869</v>
+        <v>-2.148207629890915</v>
       </c>
       <c r="O65">
-        <v>-0.3416378642611885</v>
+        <v>-0.3544542589320009</v>
       </c>
       <c r="P65">
-        <v>-1.728894646412681</v>
+        <v>-1.793753370958914</v>
       </c>
       <c r="Q65">
-        <v>-1.577894646412681</v>
+        <v>-1.642753370958914</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1536988456347189</v>
+        <v>0.1566960357912388</v>
       </c>
       <c r="T65">
-        <v>2.103149333436439</v>
+        <v>2.161570148254118</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09518583946954451</v>
+        <v>0.09369856072783288</v>
       </c>
       <c r="W65">
-        <v>0.1816866834345155</v>
+        <v>0.1819853290058512</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.576883875572997</v>
+        <v>0.567870065017169</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1728811834485907</v>
+        <v>0.1744311834485907</v>
       </c>
       <c r="C66">
-        <v>-7.374358128708572</v>
+        <v>-7.932134577957918</v>
       </c>
       <c r="D66">
-        <v>16.89365198030993</v>
+        <v>16.722703814014</v>
       </c>
       <c r="E66">
-        <v>19.87418181367709</v>
+        <v>20.2610100966305</v>
       </c>
       <c r="F66">
-        <v>24.7570101090185</v>
+        <v>25.14383839197192</v>
       </c>
       <c r="G66">
         <v>0.489</v>
@@ -6681,37 +6681,37 @@
         <v>2.823</v>
       </c>
       <c r="M66">
-        <v>4.971207629890915</v>
+        <v>5.04888274910796</v>
       </c>
       <c r="N66">
-        <v>-2.148207629890915</v>
+        <v>-2.22588274910796</v>
       </c>
       <c r="O66">
-        <v>-0.3544542589320009</v>
+        <v>-0.3672706536028134</v>
       </c>
       <c r="P66">
-        <v>-1.793753370958914</v>
+        <v>-1.858612095505147</v>
       </c>
       <c r="Q66">
-        <v>-1.642753370958914</v>
+        <v>-1.707612095505147</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1566960357912388</v>
+        <v>0.1598644939567028</v>
       </c>
       <c r="T66">
-        <v>2.161570148254118</v>
+        <v>2.223329295347093</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09369856072783288</v>
+        <v>0.09225704440894315</v>
       </c>
       <c r="W66">
-        <v>0.1819853290058512</v>
+        <v>0.1822747854826842</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.567870065017169</v>
+        <v>0.5591336024784432</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1744311834485907</v>
+        <v>0.1759811834485907</v>
       </c>
       <c r="C67">
-        <v>-7.932134577957918</v>
+        <v>-8.486486009883812</v>
       </c>
       <c r="D67">
-        <v>16.722703814014</v>
+        <v>16.55518066504152</v>
       </c>
       <c r="E67">
-        <v>20.2610100966305</v>
+        <v>20.64783837958392</v>
       </c>
       <c r="F67">
-        <v>25.14383839197192</v>
+        <v>25.53066667492533</v>
       </c>
       <c r="G67">
         <v>0.489</v>
@@ -6763,37 +6763,37 @@
         <v>2.823</v>
       </c>
       <c r="M67">
-        <v>5.04888274910796</v>
+        <v>5.126557868325007</v>
       </c>
       <c r="N67">
-        <v>-2.22588274910796</v>
+        <v>-2.303557868325006</v>
       </c>
       <c r="O67">
-        <v>-0.3672706536028134</v>
+        <v>-0.380087048273626</v>
       </c>
       <c r="P67">
-        <v>-1.858612095505147</v>
+        <v>-1.92347082005138</v>
       </c>
       <c r="Q67">
-        <v>-1.707612095505147</v>
+        <v>-1.77247082005138</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1598644939567028</v>
+        <v>0.1632193320142529</v>
       </c>
       <c r="T67">
-        <v>2.223329295347093</v>
+        <v>2.288721333445536</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.09225704440894315</v>
+        <v>0.09085921040274704</v>
       </c>
       <c r="W67">
-        <v>0.1822747854826842</v>
+        <v>0.1825554705511284</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5591336024784432</v>
+        <v>0.5506618812287698</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1759811834485907</v>
+        <v>0.1775311834485908</v>
       </c>
       <c r="C68">
-        <v>-8.486486009883812</v>
+        <v>-9.03751433602752</v>
       </c>
       <c r="D68">
-        <v>16.55518066504152</v>
+        <v>16.39098062185122</v>
       </c>
       <c r="E68">
-        <v>20.64783837958392</v>
+        <v>21.03466666253733</v>
       </c>
       <c r="F68">
-        <v>25.53066667492533</v>
+        <v>25.91749495787874</v>
       </c>
       <c r="G68">
         <v>0.489</v>
@@ -6845,37 +6845,37 @@
         <v>2.823</v>
       </c>
       <c r="M68">
-        <v>5.126557868325007</v>
+        <v>5.204232987542052</v>
       </c>
       <c r="N68">
-        <v>-2.303557868325006</v>
+        <v>-2.381232987542051</v>
       </c>
       <c r="O68">
-        <v>-0.380087048273626</v>
+        <v>-0.3929034429444385</v>
       </c>
       <c r="P68">
-        <v>-1.92347082005138</v>
+        <v>-1.988329544597613</v>
       </c>
       <c r="Q68">
-        <v>-1.77247082005138</v>
+        <v>-1.837329544597613</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1632193320142529</v>
+        <v>0.1667774935904424</v>
       </c>
       <c r="T68">
-        <v>2.288721333445536</v>
+        <v>2.358076525368129</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09085921040274704</v>
+        <v>0.08950310278479559</v>
       </c>
       <c r="W68">
-        <v>0.1825554705511284</v>
+        <v>0.1828277769608131</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5506618812287698</v>
+        <v>0.5424430471805792</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1775311834485908</v>
+        <v>0.1790811834485907</v>
       </c>
       <c r="C69">
-        <v>-9.03751433602752</v>
+        <v>-9.585317464461543</v>
       </c>
       <c r="D69">
-        <v>16.39098062185122</v>
+        <v>16.23000577637062</v>
       </c>
       <c r="E69">
-        <v>21.03466666253733</v>
+        <v>21.42149494549075</v>
       </c>
       <c r="F69">
-        <v>25.91749495787874</v>
+        <v>26.30432324083216</v>
       </c>
       <c r="G69">
         <v>0.489</v>
@@ -6927,37 +6927,37 @@
         <v>2.823</v>
       </c>
       <c r="M69">
-        <v>5.204232987542052</v>
+        <v>5.281908106759098</v>
       </c>
       <c r="N69">
-        <v>-2.381232987542051</v>
+        <v>-2.458908106759098</v>
       </c>
       <c r="O69">
-        <v>-0.3929034429444385</v>
+        <v>-0.4057198376152512</v>
       </c>
       <c r="P69">
-        <v>-1.988329544597613</v>
+        <v>-2.053188269143846</v>
       </c>
       <c r="Q69">
-        <v>-1.837329544597613</v>
+        <v>-1.902188269143846</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1667774935904424</v>
+        <v>0.1705580402651437</v>
       </c>
       <c r="T69">
-        <v>2.358076525368129</v>
+        <v>2.431766416785882</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08950310278479559</v>
+        <v>0.08818688068501918</v>
       </c>
       <c r="W69">
-        <v>0.1828277769608131</v>
+        <v>0.1830920743584482</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5424430471805792</v>
+        <v>0.5344659435455708</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1790811834485907</v>
+        <v>0.1806311834485907</v>
       </c>
       <c r="C70">
-        <v>-9.585317464461543</v>
+        <v>-10.1299894944669</v>
       </c>
       <c r="D70">
-        <v>16.23000577637062</v>
+        <v>16.07216202931867</v>
       </c>
       <c r="E70">
-        <v>21.42149494549075</v>
+        <v>21.80832322844416</v>
       </c>
       <c r="F70">
-        <v>26.30432324083216</v>
+        <v>26.69115152378557</v>
       </c>
       <c r="G70">
         <v>0.489</v>
@@ -7009,37 +7009,37 @@
         <v>2.823</v>
       </c>
       <c r="M70">
-        <v>5.281908106759098</v>
+        <v>5.359583225976143</v>
       </c>
       <c r="N70">
-        <v>-2.458908106759098</v>
+        <v>-2.536583225976143</v>
       </c>
       <c r="O70">
-        <v>-0.4057198376152512</v>
+        <v>-0.4185362322860636</v>
       </c>
       <c r="P70">
-        <v>-2.053188269143846</v>
+        <v>-2.118046993690079</v>
       </c>
       <c r="Q70">
-        <v>-1.902188269143846</v>
+        <v>-1.967046993690079</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1705580402651437</v>
+        <v>0.1745824931769225</v>
       </c>
       <c r="T70">
-        <v>2.431766416785882</v>
+        <v>2.510210494746718</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08818688068501918</v>
+        <v>0.08690880995045369</v>
       </c>
       <c r="W70">
-        <v>0.1830920743584482</v>
+        <v>0.1833487109619489</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5344659435455708</v>
+        <v>0.5267200603057798</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1806311834485907</v>
+        <v>0.1821811834485907</v>
       </c>
       <c r="C71">
-        <v>-10.1299894944669</v>
+        <v>-10.67162089995985</v>
       </c>
       <c r="D71">
-        <v>16.07216202931867</v>
+        <v>15.91735890677914</v>
       </c>
       <c r="E71">
-        <v>21.80832322844416</v>
+        <v>22.19515151139758</v>
       </c>
       <c r="F71">
-        <v>26.69115152378557</v>
+        <v>27.07797980673899</v>
       </c>
       <c r="G71">
         <v>0.489</v>
@@ -7091,37 +7091,37 @@
         <v>2.823</v>
       </c>
       <c r="M71">
-        <v>5.359583225976143</v>
+        <v>5.437258345193189</v>
       </c>
       <c r="N71">
-        <v>-2.536583225976143</v>
+        <v>-2.614258345193188</v>
       </c>
       <c r="O71">
-        <v>-0.4185362322860636</v>
+        <v>-0.4313526269568761</v>
       </c>
       <c r="P71">
-        <v>-2.118046993690079</v>
+        <v>-2.182905718236312</v>
       </c>
       <c r="Q71">
-        <v>-1.967046993690079</v>
+        <v>-2.031905718236312</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1745824931769225</v>
+        <v>0.1788752429494866</v>
       </c>
       <c r="T71">
-        <v>2.510210494746718</v>
+        <v>2.593884177904942</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08690880995045369</v>
+        <v>0.08566725552259007</v>
       </c>
       <c r="W71">
-        <v>0.1833487109619489</v>
+        <v>0.1835980150910639</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5267200603057798</v>
+        <v>0.5191954880156973</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1821811834485907</v>
+        <v>0.1837311834485907</v>
       </c>
       <c r="C72">
-        <v>-10.67162089995985</v>
+        <v>-11.21029870241935</v>
       </c>
       <c r="D72">
-        <v>15.91735890677914</v>
+        <v>15.76550938727305</v>
       </c>
       <c r="E72">
-        <v>22.19515151139758</v>
+        <v>22.58197979435099</v>
       </c>
       <c r="F72">
-        <v>27.07797980673899</v>
+        <v>27.4648080896924</v>
       </c>
       <c r="G72">
         <v>0.489</v>
@@ -7173,37 +7173,37 @@
         <v>2.823</v>
       </c>
       <c r="M72">
-        <v>5.437258345193189</v>
+        <v>5.514933464410235</v>
       </c>
       <c r="N72">
-        <v>-2.614258345193188</v>
+        <v>-2.691933464410234</v>
       </c>
       <c r="O72">
-        <v>-0.4313526269568761</v>
+        <v>-0.4441690216276887</v>
       </c>
       <c r="P72">
-        <v>-2.182905718236312</v>
+        <v>-2.247764442782546</v>
       </c>
       <c r="Q72">
-        <v>-2.031905718236312</v>
+        <v>-2.096764442782546</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1788752429494866</v>
+        <v>0.1834640444305034</v>
       </c>
       <c r="T72">
-        <v>2.593884177904942</v>
+        <v>2.683328459901664</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08566725552259007</v>
+        <v>0.0844606744588916</v>
       </c>
       <c r="W72">
-        <v>0.1835980150910639</v>
+        <v>0.1838402965686546</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5191954880156973</v>
+        <v>0.5118828755084339</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1837311834485907</v>
+        <v>0.1852811834485907</v>
       </c>
       <c r="C73">
-        <v>-11.21029870241935</v>
+        <v>-11.74610663400998</v>
       </c>
       <c r="D73">
-        <v>15.76550938727305</v>
+        <v>15.61652973863583</v>
       </c>
       <c r="E73">
-        <v>22.58197979435099</v>
+        <v>22.9688080773044</v>
       </c>
       <c r="F73">
-        <v>27.4648080896924</v>
+        <v>27.85163637264581</v>
       </c>
       <c r="G73">
         <v>0.489</v>
@@ -7255,37 +7255,37 @@
         <v>2.823</v>
       </c>
       <c r="M73">
-        <v>5.514933464410234</v>
+        <v>5.592608583627279</v>
       </c>
       <c r="N73">
-        <v>-2.691933464410234</v>
+        <v>-2.769608583627279</v>
       </c>
       <c r="O73">
-        <v>-0.4441690216276886</v>
+        <v>-0.456985416298501</v>
       </c>
       <c r="P73">
-        <v>-2.247764442782545</v>
+        <v>-2.312623167328778</v>
       </c>
       <c r="Q73">
-        <v>-2.096764442782545</v>
+        <v>-2.161623167328778</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1834640444305034</v>
+        <v>0.1883806174458785</v>
       </c>
       <c r="T73">
-        <v>2.683328459901663</v>
+        <v>2.779161619183865</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08446067445889162</v>
+        <v>0.08328760953585146</v>
       </c>
       <c r="W73">
-        <v>0.1838402965686546</v>
+        <v>0.184075848005201</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5118828755084339</v>
+        <v>0.5047733911263724</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1852811834485907</v>
+        <v>0.2127592015499599</v>
       </c>
       <c r="C74">
-        <v>-11.74610663400998</v>
+        <v>-14.37367761990641</v>
       </c>
       <c r="D74">
-        <v>15.61652973863583</v>
+        <v>13.37578703569282</v>
       </c>
       <c r="E74">
-        <v>22.9688080773044</v>
+        <v>23.35563636025782</v>
       </c>
       <c r="F74">
-        <v>27.85163637264581</v>
+        <v>28.23846465559923</v>
       </c>
       <c r="G74">
         <v>0.489</v>
@@ -7337,45 +7337,45 @@
         <v>2.823</v>
       </c>
       <c r="M74">
-        <v>5.592608583627279</v>
+        <v>6.658629965790298</v>
       </c>
       <c r="N74">
-        <v>-2.769608583627279</v>
+        <v>-3.835629965790297</v>
       </c>
       <c r="O74">
-        <v>-0.456985416298501</v>
+        <v>-0.6328789443553992</v>
       </c>
       <c r="P74">
-        <v>-2.312623167328778</v>
+        <v>-3.202751021434898</v>
       </c>
       <c r="Q74">
-        <v>-2.161623167328778</v>
+        <v>-3.051751021434899</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1883806174458785</v>
+        <v>0.1950614480970934</v>
       </c>
       <c r="T74">
-        <v>2.779161619183865</v>
+        <v>2.909383443599595</v>
       </c>
       <c r="U74">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08328760953585146</v>
+        <v>0.06995357939892909</v>
       </c>
       <c r="W74">
-        <v>0.184075848005201</v>
+        <v>0.2193049459777325</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5047733911263724</v>
+        <v>0.4239610872662369</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2127592015499599</v>
+        <v>0.21465920154996</v>
       </c>
       <c r="C75">
-        <v>-14.37367761990641</v>
+        <v>-14.89190954354554</v>
       </c>
       <c r="D75">
-        <v>13.37578703569282</v>
+        <v>13.24438339500711</v>
       </c>
       <c r="E75">
-        <v>23.35563636025782</v>
+        <v>23.74246464321123</v>
       </c>
       <c r="F75">
-        <v>28.23846465559923</v>
+        <v>28.62529293855264</v>
       </c>
       <c r="G75">
         <v>0.489</v>
@@ -7419,37 +7419,37 @@
         <v>2.823</v>
       </c>
       <c r="M75">
-        <v>6.658629965790298</v>
+        <v>6.749844074910714</v>
       </c>
       <c r="N75">
-        <v>-3.835629965790297</v>
+        <v>-3.926844074910713</v>
       </c>
       <c r="O75">
-        <v>-0.6328789443553992</v>
+        <v>-0.6479292723602678</v>
       </c>
       <c r="P75">
-        <v>-3.202751021434898</v>
+        <v>-3.278914802550446</v>
       </c>
       <c r="Q75">
-        <v>-3.051751021434899</v>
+        <v>-3.127914802550446</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1950614480970934</v>
+        <v>0.2008022730239047</v>
       </c>
       <c r="T75">
-        <v>2.909383443599595</v>
+        <v>3.021282806814964</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06995357939892909</v>
+        <v>0.06900826075840301</v>
       </c>
       <c r="W75">
-        <v>0.2193049459777325</v>
+        <v>0.2195278521131686</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4239610872662369</v>
+        <v>0.4182318833842606</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.21465920154996</v>
+        <v>0.2165592015499599</v>
       </c>
       <c r="C76">
-        <v>-14.89190954354554</v>
+        <v>-15.40758476724621</v>
       </c>
       <c r="D76">
-        <v>13.24438339500711</v>
+        <v>13.11553645425984</v>
       </c>
       <c r="E76">
-        <v>23.74246464321123</v>
+        <v>24.12929292616464</v>
       </c>
       <c r="F76">
-        <v>28.62529293855264</v>
+        <v>29.01212122150606</v>
       </c>
       <c r="G76">
         <v>0.489</v>
@@ -7501,37 +7501,37 @@
         <v>2.823</v>
       </c>
       <c r="M76">
-        <v>6.749844074910714</v>
+        <v>6.841058184031128</v>
       </c>
       <c r="N76">
-        <v>-3.926844074910713</v>
+        <v>-4.018058184031128</v>
       </c>
       <c r="O76">
-        <v>-0.6479292723602678</v>
+        <v>-0.6629796003651361</v>
       </c>
       <c r="P76">
-        <v>-3.278914802550446</v>
+        <v>-3.355078583665992</v>
       </c>
       <c r="Q76">
-        <v>-3.127914802550446</v>
+        <v>-3.204078583665992</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2008022730239047</v>
+        <v>0.2070023639448609</v>
       </c>
       <c r="T76">
-        <v>3.021282806814964</v>
+        <v>3.142134119087563</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06900826075840301</v>
+        <v>0.06808815061495764</v>
       </c>
       <c r="W76">
-        <v>0.2195278521131686</v>
+        <v>0.219744814084993</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4182318833842606</v>
+        <v>0.4126554582724705</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2165592015499599</v>
+        <v>0.21845920154996</v>
       </c>
       <c r="C77">
-        <v>-15.40758476724621</v>
+        <v>-15.9207771900494</v>
       </c>
       <c r="D77">
-        <v>13.11553645425984</v>
+        <v>12.98917231441007</v>
       </c>
       <c r="E77">
-        <v>24.12929292616464</v>
+        <v>24.51612120911806</v>
       </c>
       <c r="F77">
-        <v>29.01212122150606</v>
+        <v>29.39894950445947</v>
       </c>
       <c r="G77">
         <v>0.489</v>
@@ -7583,37 +7583,37 @@
         <v>2.823</v>
       </c>
       <c r="M77">
-        <v>6.841058184031128</v>
+        <v>6.932272293151543</v>
       </c>
       <c r="N77">
-        <v>-4.018058184031128</v>
+        <v>-4.109272293151543</v>
       </c>
       <c r="O77">
-        <v>-0.6629796003651361</v>
+        <v>-0.6780299283700046</v>
       </c>
       <c r="P77">
-        <v>-3.355078583665992</v>
+        <v>-3.431242364781538</v>
       </c>
       <c r="Q77">
-        <v>-3.204078583665992</v>
+        <v>-3.280242364781539</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2070023639448609</v>
+        <v>0.2137191291092301</v>
       </c>
       <c r="T77">
-        <v>3.142134119087563</v>
+        <v>3.273056374049545</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06808815061495764</v>
+        <v>0.06719225389633977</v>
       </c>
       <c r="W77">
-        <v>0.219744814084993</v>
+        <v>0.2199560665312431</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4126554582724705</v>
+        <v>0.407225781189938</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.21845920154996</v>
+        <v>0.22035920154996</v>
       </c>
       <c r="C78">
-        <v>-15.9207771900494</v>
+        <v>-16.43155789019595</v>
       </c>
       <c r="D78">
-        <v>12.98917231441007</v>
+        <v>12.86521989721694</v>
       </c>
       <c r="E78">
-        <v>24.51612120911806</v>
+        <v>24.90294949207147</v>
       </c>
       <c r="F78">
-        <v>29.39894950445947</v>
+        <v>29.78577778741289</v>
       </c>
       <c r="G78">
         <v>0.489</v>
@@ -7665,37 +7665,37 @@
         <v>2.823</v>
       </c>
       <c r="M78">
-        <v>6.932272293151543</v>
+        <v>7.023486402271959</v>
       </c>
       <c r="N78">
-        <v>-4.109272293151543</v>
+        <v>-4.200486402271959</v>
       </c>
       <c r="O78">
-        <v>-0.6780299283700046</v>
+        <v>-0.6930802563748732</v>
       </c>
       <c r="P78">
-        <v>-3.431242364781538</v>
+        <v>-3.507406145897085</v>
       </c>
       <c r="Q78">
-        <v>-3.280242364781539</v>
+        <v>-3.356406145897085</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2137191291092301</v>
+        <v>0.2210199608096314</v>
       </c>
       <c r="T78">
-        <v>3.273056374049545</v>
+        <v>3.415363172921264</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06719225389633977</v>
+        <v>0.06631962722236133</v>
       </c>
       <c r="W78">
-        <v>0.2199560665312431</v>
+        <v>0.2201618319009672</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.407225781189938</v>
+        <v>0.4019371346809778</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.22035920154996</v>
+        <v>0.22225920154996</v>
       </c>
       <c r="C79">
-        <v>-16.43155789019595</v>
+        <v>-16.93999525844525</v>
       </c>
       <c r="D79">
-        <v>12.86521989721694</v>
+        <v>12.74361081192105</v>
       </c>
       <c r="E79">
-        <v>24.90294949207147</v>
+        <v>25.28977777502489</v>
       </c>
       <c r="F79">
-        <v>29.78577778741289</v>
+        <v>30.1726060703663</v>
       </c>
       <c r="G79">
         <v>0.489</v>
@@ -7747,37 +7747,37 @@
         <v>2.823</v>
       </c>
       <c r="M79">
-        <v>7.023486402271959</v>
+        <v>7.114700511392374</v>
       </c>
       <c r="N79">
-        <v>-4.200486402271959</v>
+        <v>-4.291700511392373</v>
       </c>
       <c r="O79">
-        <v>-0.6930802563748732</v>
+        <v>-0.7081305843797416</v>
       </c>
       <c r="P79">
-        <v>-3.507406145897085</v>
+        <v>-3.583569927012632</v>
       </c>
       <c r="Q79">
-        <v>-3.356406145897085</v>
+        <v>-3.432569927012632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2210199608096314</v>
+        <v>0.2289845044827965</v>
       </c>
       <c r="T79">
-        <v>3.415363172921264</v>
+        <v>3.570606953508595</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06631962722236133</v>
+        <v>0.06546937559130543</v>
       </c>
       <c r="W79">
-        <v>0.2201618319009672</v>
+        <v>0.2203623212355702</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4019371346809778</v>
+        <v>0.3967840944927601</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.22225920154996</v>
+        <v>0.22415920154996</v>
       </c>
       <c r="C80">
-        <v>-16.93999525844525</v>
+        <v>-17.44615512390362</v>
       </c>
       <c r="D80">
-        <v>12.74361081192105</v>
+        <v>12.62427922941609</v>
       </c>
       <c r="E80">
-        <v>25.28977777502489</v>
+        <v>25.6766060579783</v>
       </c>
       <c r="F80">
-        <v>30.1726060703663</v>
+        <v>30.55943435331972</v>
       </c>
       <c r="G80">
         <v>0.489</v>
@@ -7829,37 +7829,37 @@
         <v>2.823</v>
       </c>
       <c r="M80">
-        <v>7.114700511392374</v>
+        <v>7.20591462051279</v>
       </c>
       <c r="N80">
-        <v>-4.291700511392373</v>
+        <v>-4.382914620512789</v>
       </c>
       <c r="O80">
-        <v>-0.7081305843797416</v>
+        <v>-0.7231809123846102</v>
       </c>
       <c r="P80">
-        <v>-3.583569927012632</v>
+        <v>-3.659733708128179</v>
       </c>
       <c r="Q80">
-        <v>-3.432569927012632</v>
+        <v>-3.508733708128179</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2289845044827965</v>
+        <v>0.2377075761248344</v>
       </c>
       <c r="T80">
-        <v>3.570606953508595</v>
+        <v>3.740635856056623</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06546937559130543</v>
+        <v>0.06464064931799776</v>
       </c>
       <c r="W80">
-        <v>0.2203623212355702</v>
+        <v>0.2205577348908161</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3967840944927601</v>
+        <v>0.3917615110181681</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.22415920154996</v>
+        <v>0.22605920154996</v>
       </c>
       <c r="C81">
-        <v>-17.44615512390362</v>
+        <v>-17.9501008728486</v>
       </c>
       <c r="D81">
-        <v>12.62427922941609</v>
+        <v>12.50716176342452</v>
       </c>
       <c r="E81">
-        <v>25.6766060579783</v>
+        <v>26.06343434093172</v>
       </c>
       <c r="F81">
-        <v>30.55943435331972</v>
+        <v>30.94626263627313</v>
       </c>
       <c r="G81">
         <v>0.489</v>
@@ -7911,37 +7911,37 @@
         <v>2.823</v>
       </c>
       <c r="M81">
-        <v>7.20591462051279</v>
+        <v>7.297128729633204</v>
       </c>
       <c r="N81">
-        <v>-4.382914620512789</v>
+        <v>-4.474128729633204</v>
       </c>
       <c r="O81">
-        <v>-0.7231809123846102</v>
+        <v>-0.7382312403894787</v>
       </c>
       <c r="P81">
-        <v>-3.659733708128179</v>
+        <v>-3.735897489243725</v>
       </c>
       <c r="Q81">
-        <v>-3.508733708128179</v>
+        <v>-3.584897489243725</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2377075761248344</v>
+        <v>0.2473029549310761</v>
       </c>
       <c r="T81">
-        <v>3.740635856056623</v>
+        <v>3.927667648859454</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06464064931799776</v>
+        <v>0.06383264120152278</v>
       </c>
       <c r="W81">
-        <v>0.2205577348908161</v>
+        <v>0.2207482632046809</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3917615110181681</v>
+        <v>0.3868644921304411</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.22605920154996</v>
+        <v>0.22795920154996</v>
       </c>
       <c r="C82">
-        <v>-17.9501008728486</v>
+        <v>-18.45189356099998</v>
       </c>
       <c r="D82">
-        <v>12.50716176342452</v>
+        <v>12.39219735822656</v>
       </c>
       <c r="E82">
-        <v>26.06343434093172</v>
+        <v>26.45026262388513</v>
       </c>
       <c r="F82">
-        <v>30.94626263627313</v>
+        <v>31.33309091922654</v>
       </c>
       <c r="G82">
         <v>0.489</v>
@@ -7993,37 +7993,37 @@
         <v>2.823</v>
       </c>
       <c r="M82">
-        <v>7.297128729633204</v>
+        <v>7.388342838753619</v>
       </c>
       <c r="N82">
-        <v>-4.474128729633204</v>
+        <v>-4.565342838753619</v>
       </c>
       <c r="O82">
-        <v>-0.7382312403894787</v>
+        <v>-0.7532815683943471</v>
       </c>
       <c r="P82">
-        <v>-3.735897489243725</v>
+        <v>-3.812061270359272</v>
       </c>
       <c r="Q82">
-        <v>-3.584897489243725</v>
+        <v>-3.661061270359272</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2473029549310761</v>
+        <v>0.257908373611659</v>
       </c>
       <c r="T82">
-        <v>3.927667648859454</v>
+        <v>4.134386998799426</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06383264120152278</v>
+        <v>0.06304458390273855</v>
       </c>
       <c r="W82">
-        <v>0.2207482632046809</v>
+        <v>0.2209340871157343</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3868644921304411</v>
+        <v>0.3820883872893246</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.22795920154996</v>
+        <v>0.22985920154996</v>
       </c>
       <c r="C83">
-        <v>-18.45189356099998</v>
+        <v>-18.95159201965534</v>
       </c>
       <c r="D83">
-        <v>12.39219735822656</v>
+        <v>12.27932718252462</v>
       </c>
       <c r="E83">
-        <v>26.45026262388513</v>
+        <v>26.83709090683855</v>
       </c>
       <c r="F83">
-        <v>31.33309091922654</v>
+        <v>31.71991920217996</v>
       </c>
       <c r="G83">
         <v>0.489</v>
@@ -8075,37 +8075,37 @@
         <v>2.823</v>
       </c>
       <c r="M83">
-        <v>7.388342838753619</v>
+        <v>7.479556947874035</v>
       </c>
       <c r="N83">
-        <v>-4.565342838753619</v>
+        <v>-4.656556947874035</v>
       </c>
       <c r="O83">
-        <v>-0.7532815683943471</v>
+        <v>-0.7683318963992157</v>
       </c>
       <c r="P83">
-        <v>-3.812061270359272</v>
+        <v>-3.888225051474819</v>
       </c>
       <c r="Q83">
-        <v>-3.661061270359272</v>
+        <v>-3.737225051474819</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.257908373611659</v>
+        <v>0.2696921721456401</v>
       </c>
       <c r="T83">
-        <v>4.134386998799426</v>
+        <v>4.364075165399394</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06304458390273855</v>
+        <v>0.06227574751368076</v>
       </c>
       <c r="W83">
-        <v>0.2209340871157343</v>
+        <v>0.2211153787362741</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3820883872893246</v>
+        <v>0.3774287728101864</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.22985920154996</v>
+        <v>0.23175920154996</v>
       </c>
       <c r="C84">
-        <v>-18.95159201965534</v>
+        <v>-19.44925295607765</v>
       </c>
       <c r="D84">
-        <v>12.27932718252462</v>
+        <v>12.16849452905573</v>
       </c>
       <c r="E84">
-        <v>26.83709090683855</v>
+        <v>27.22391918979196</v>
       </c>
       <c r="F84">
-        <v>31.71991920217996</v>
+        <v>32.10674748513338</v>
       </c>
       <c r="G84">
         <v>0.489</v>
@@ -8157,37 +8157,37 @@
         <v>2.823</v>
       </c>
       <c r="M84">
-        <v>7.479556947874035</v>
+        <v>7.570771056994451</v>
       </c>
       <c r="N84">
-        <v>-4.656556947874035</v>
+        <v>-4.74777105699445</v>
       </c>
       <c r="O84">
-        <v>-0.7683318963992157</v>
+        <v>-0.7833822244040843</v>
       </c>
       <c r="P84">
-        <v>-3.888225051474819</v>
+        <v>-3.964388832590366</v>
       </c>
       <c r="Q84">
-        <v>-3.737225051474819</v>
+        <v>-3.813388832590366</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2696921721456401</v>
+        <v>0.2828622999189131</v>
       </c>
       <c r="T84">
-        <v>4.364075165399394</v>
+        <v>4.620785469246417</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06227574751368076</v>
+        <v>0.06152543730267255</v>
       </c>
       <c r="W84">
-        <v>0.2211153787362741</v>
+        <v>0.2212923018840298</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3774287728101864</v>
+        <v>0.3728814381980154</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.23175920154996</v>
+        <v>0.23365920154996</v>
       </c>
       <c r="C85">
-        <v>-19.44925295607765</v>
+        <v>-19.94493104849511</v>
       </c>
       <c r="D85">
-        <v>12.16849452905573</v>
+        <v>12.05964471959168</v>
       </c>
       <c r="E85">
-        <v>27.22391918979196</v>
+        <v>27.61074747274537</v>
       </c>
       <c r="F85">
-        <v>32.10674748513338</v>
+        <v>32.49357576808679</v>
       </c>
       <c r="G85">
         <v>0.489</v>
@@ -8239,37 +8239,37 @@
         <v>2.823</v>
       </c>
       <c r="M85">
-        <v>7.570771056994451</v>
+        <v>7.661985166114865</v>
       </c>
       <c r="N85">
-        <v>-4.74777105699445</v>
+        <v>-4.838985166114864</v>
       </c>
       <c r="O85">
-        <v>-0.7833822244040843</v>
+        <v>-0.7984325524089526</v>
       </c>
       <c r="P85">
-        <v>-3.964388832590366</v>
+        <v>-4.040552613705912</v>
       </c>
       <c r="Q85">
-        <v>-3.813388832590366</v>
+        <v>-3.889552613705912</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2828622999189131</v>
+        <v>0.2976786936638453</v>
       </c>
       <c r="T85">
-        <v>4.620785469246417</v>
+        <v>4.90958456107432</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06152543730267255</v>
+        <v>0.06079299162049789</v>
       </c>
       <c r="W85">
-        <v>0.2212923018840298</v>
+        <v>0.2214650125758866</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3728814381980154</v>
+        <v>0.3684423734575629</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2336592015499599</v>
+        <v>0.23555920154996</v>
       </c>
       <c r="C86">
-        <v>-19.9449310484951</v>
+        <v>-20.43867903604727</v>
       </c>
       <c r="D86">
-        <v>12.05964471959168</v>
+        <v>11.95272501499293</v>
       </c>
       <c r="E86">
-        <v>27.61074747274537</v>
+        <v>27.99757575569878</v>
       </c>
       <c r="F86">
-        <v>32.49357576808679</v>
+        <v>32.88040405104019</v>
       </c>
       <c r="G86">
         <v>0.489</v>
@@ -8321,37 +8321,37 @@
         <v>2.823</v>
       </c>
       <c r="M86">
-        <v>7.661985166114865</v>
+        <v>7.753199275235279</v>
       </c>
       <c r="N86">
-        <v>-4.838985166114864</v>
+        <v>-4.930199275235278</v>
       </c>
       <c r="O86">
-        <v>-0.7984325524089526</v>
+        <v>-0.8134828804138209</v>
       </c>
       <c r="P86">
-        <v>-4.040552613705912</v>
+        <v>-4.116716394821458</v>
       </c>
       <c r="Q86">
-        <v>-3.889552613705912</v>
+        <v>-3.965716394821458</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.297678693663845</v>
+        <v>0.3144706065747681</v>
       </c>
       <c r="T86">
-        <v>4.909584561074317</v>
+        <v>5.236890198479271</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06079299162049789</v>
+        <v>0.06007777995437439</v>
       </c>
       <c r="W86">
-        <v>0.2214650125758866</v>
+        <v>0.2216336594867585</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3684423734575629</v>
+        <v>0.3641077572992387</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.23555920154996</v>
+        <v>0.23745920154996</v>
       </c>
       <c r="C87">
-        <v>-20.43867903604727</v>
+        <v>-20.93054780398855</v>
       </c>
       <c r="D87">
-        <v>11.95272501499293</v>
+        <v>11.84768453000506</v>
       </c>
       <c r="E87">
-        <v>27.99757575569878</v>
+        <v>28.3844040386522</v>
       </c>
       <c r="F87">
-        <v>32.88040405104019</v>
+        <v>33.26723233399361</v>
       </c>
       <c r="G87">
         <v>0.489</v>
@@ -8403,37 +8403,37 @@
         <v>2.823</v>
       </c>
       <c r="M87">
-        <v>7.753199275235279</v>
+        <v>7.844413384355694</v>
       </c>
       <c r="N87">
-        <v>-4.930199275235278</v>
+        <v>-5.021413384355694</v>
       </c>
       <c r="O87">
-        <v>-0.8134828804138209</v>
+        <v>-0.8285332084186895</v>
       </c>
       <c r="P87">
-        <v>-4.116716394821458</v>
+        <v>-4.192880175937004</v>
       </c>
       <c r="Q87">
-        <v>-3.965716394821458</v>
+        <v>-4.041880175937004</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3144706065747681</v>
+        <v>0.3336613641872515</v>
       </c>
       <c r="T87">
-        <v>5.236890198479271</v>
+        <v>5.610953784084933</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06007777995437439</v>
+        <v>0.05937920111769561</v>
       </c>
       <c r="W87">
-        <v>0.2216336594867585</v>
+        <v>0.2217983843764474</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3641077572992387</v>
+        <v>0.3598739461678522</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.23745920154996</v>
+        <v>0.23935920154996</v>
       </c>
       <c r="C88">
-        <v>-20.93054780398855</v>
+        <v>-21.42058646443828</v>
       </c>
       <c r="D88">
-        <v>11.84768453000506</v>
+        <v>11.74447415250875</v>
       </c>
       <c r="E88">
-        <v>28.3844040386522</v>
+        <v>28.77123232160562</v>
       </c>
       <c r="F88">
-        <v>33.26723233399361</v>
+        <v>33.65406061694703</v>
       </c>
       <c r="G88">
         <v>0.489</v>
@@ -8485,37 +8485,37 @@
         <v>2.823</v>
       </c>
       <c r="M88">
-        <v>7.844413384355694</v>
+        <v>7.93562749347611</v>
       </c>
       <c r="N88">
-        <v>-5.021413384355694</v>
+        <v>-5.11262749347611</v>
       </c>
       <c r="O88">
-        <v>-0.8285332084186895</v>
+        <v>-0.8435835364235581</v>
       </c>
       <c r="P88">
-        <v>-4.192880175937004</v>
+        <v>-4.269043957052552</v>
       </c>
       <c r="Q88">
-        <v>-4.041880175937004</v>
+        <v>-4.118043957052552</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3336613641872515</v>
+        <v>0.3558045460478093</v>
       </c>
       <c r="T88">
-        <v>5.610953784084933</v>
+        <v>6.042565613629928</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05937920111769561</v>
+        <v>0.05869668156461864</v>
       </c>
       <c r="W88">
-        <v>0.2217983843764474</v>
+        <v>0.2219593224870629</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3598739461678522</v>
+        <v>0.3557374640279918</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.23935920154996</v>
+        <v>0.24125920154996</v>
       </c>
       <c r="C89">
-        <v>-21.42058646443828</v>
+        <v>-21.90884243294646</v>
       </c>
       <c r="D89">
-        <v>11.74447415250875</v>
+        <v>11.64304646695398</v>
       </c>
       <c r="E89">
-        <v>28.77123232160562</v>
+        <v>29.15806060455903</v>
       </c>
       <c r="F89">
-        <v>33.65406061694703</v>
+        <v>34.04088889990044</v>
       </c>
       <c r="G89">
         <v>0.489</v>
@@ -8567,37 +8567,37 @@
         <v>2.823</v>
       </c>
       <c r="M89">
-        <v>7.93562749347611</v>
+        <v>8.026841602596523</v>
       </c>
       <c r="N89">
-        <v>-5.11262749347611</v>
+        <v>-5.203841602596523</v>
       </c>
       <c r="O89">
-        <v>-0.8435835364235581</v>
+        <v>-0.8586338644284263</v>
       </c>
       <c r="P89">
-        <v>-4.269043957052552</v>
+        <v>-4.345207738168097</v>
       </c>
       <c r="Q89">
-        <v>-4.118043957052552</v>
+        <v>-4.194207738168097</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3558045460478093</v>
+        <v>0.3816382582184601</v>
       </c>
       <c r="T89">
-        <v>6.042565613629928</v>
+        <v>6.54611274809909</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05869668156461864</v>
+        <v>0.05802967381956618</v>
       </c>
       <c r="W89">
-        <v>0.2219593224870629</v>
+        <v>0.2221166029133463</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3557374640279918</v>
+        <v>0.3516949928458556</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.24125920154996</v>
+        <v>0.24315920154996</v>
       </c>
       <c r="C90">
-        <v>-21.90884243294646</v>
+        <v>-22.39536150112614</v>
       </c>
       <c r="D90">
-        <v>11.64304646695398</v>
+        <v>11.54335568172772</v>
       </c>
       <c r="E90">
-        <v>29.15806060455903</v>
+        <v>29.54488888751244</v>
       </c>
       <c r="F90">
-        <v>34.04088889990044</v>
+        <v>34.42771718285385</v>
       </c>
       <c r="G90">
         <v>0.489</v>
@@ -8649,37 +8649,37 @@
         <v>2.823</v>
       </c>
       <c r="M90">
-        <v>8.026841602596523</v>
+        <v>8.11805571171694</v>
       </c>
       <c r="N90">
-        <v>-5.203841602596523</v>
+        <v>-5.295055711716939</v>
       </c>
       <c r="O90">
-        <v>-0.8586338644284263</v>
+        <v>-0.873684192433295</v>
       </c>
       <c r="P90">
-        <v>-4.345207738168097</v>
+        <v>-4.421371519283644</v>
       </c>
       <c r="Q90">
-        <v>-4.194207738168097</v>
+        <v>-4.270371519283644</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3816382582184601</v>
+        <v>0.4121690089655929</v>
       </c>
       <c r="T90">
-        <v>6.54611274809909</v>
+        <v>7.14121390701719</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05802967381956618</v>
+        <v>0.05737765501260475</v>
       </c>
       <c r="W90">
-        <v>0.2221166029133463</v>
+        <v>0.2222703489480278</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3516949928458556</v>
+        <v>0.347743363712756</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.24315920154996</v>
+        <v>0.24505920154996</v>
       </c>
       <c r="C91">
-        <v>-22.39536150112614</v>
+        <v>-22.880187905586</v>
       </c>
       <c r="D91">
-        <v>11.54335568172772</v>
+        <v>11.44535756022127</v>
       </c>
       <c r="E91">
-        <v>29.54488888751244</v>
+        <v>29.93171717046586</v>
       </c>
       <c r="F91">
-        <v>34.42771718285385</v>
+        <v>34.81454546580727</v>
       </c>
       <c r="G91">
         <v>0.489</v>
@@ -8731,37 +8731,37 @@
         <v>2.823</v>
       </c>
       <c r="M91">
-        <v>8.11805571171694</v>
+        <v>8.209269820837354</v>
       </c>
       <c r="N91">
-        <v>-5.295055711716939</v>
+        <v>-5.386269820837354</v>
       </c>
       <c r="O91">
-        <v>-0.873684192433295</v>
+        <v>-0.8887345204381635</v>
       </c>
       <c r="P91">
-        <v>-4.421371519283644</v>
+        <v>-4.497535300399191</v>
       </c>
       <c r="Q91">
-        <v>-4.270371519283644</v>
+        <v>-4.346535300399191</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4121690089655929</v>
+        <v>0.4488059098621522</v>
       </c>
       <c r="T91">
-        <v>7.14121390701719</v>
+        <v>7.855335297718909</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05737765501260475</v>
+        <v>0.0567401255124647</v>
       </c>
       <c r="W91">
-        <v>0.2222703489480278</v>
+        <v>0.2224206784041609</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.347743363712756</v>
+        <v>0.3438795485603922</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.24505920154996</v>
+        <v>0.24695920154996</v>
       </c>
       <c r="C92">
-        <v>-22.880187905586</v>
+        <v>-23.36336439338133</v>
       </c>
       <c r="D92">
-        <v>11.44535756022127</v>
+        <v>11.34900935537935</v>
       </c>
       <c r="E92">
-        <v>29.93171717046586</v>
+        <v>30.31854545341927</v>
       </c>
       <c r="F92">
-        <v>34.81454546580727</v>
+        <v>35.20137374876068</v>
       </c>
       <c r="G92">
         <v>0.489</v>
@@ -8813,37 +8813,37 @@
         <v>2.823</v>
       </c>
       <c r="M92">
-        <v>8.209269820837354</v>
+        <v>8.300483929957769</v>
       </c>
       <c r="N92">
-        <v>-5.386269820837354</v>
+        <v>-5.477483929957769</v>
       </c>
       <c r="O92">
-        <v>-0.8887345204381635</v>
+        <v>-0.9037848484430319</v>
       </c>
       <c r="P92">
-        <v>-4.497535300399191</v>
+        <v>-4.573699081514737</v>
       </c>
       <c r="Q92">
-        <v>-4.346535300399191</v>
+        <v>-4.422699081514737</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4488059098621522</v>
+        <v>0.4935843442912803</v>
       </c>
       <c r="T92">
-        <v>7.855335297718909</v>
+        <v>8.728150330798789</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0567401255124647</v>
+        <v>0.05611660764969036</v>
       </c>
       <c r="W92">
-        <v>0.2224206784041609</v>
+        <v>0.222567703916203</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3438795485603922</v>
+        <v>0.3401006524223659</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.24695920154996</v>
+        <v>0.24885920154996</v>
       </c>
       <c r="C93">
-        <v>-23.36336439338133</v>
+        <v>-23.84493228418672</v>
       </c>
       <c r="D93">
-        <v>11.34900935537935</v>
+        <v>11.25426974752737</v>
       </c>
       <c r="E93">
-        <v>30.31854545341927</v>
+        <v>30.70537373637269</v>
       </c>
       <c r="F93">
-        <v>35.20137374876068</v>
+        <v>35.5882020317141</v>
       </c>
       <c r="G93">
         <v>0.489</v>
@@ -8895,37 +8895,37 @@
         <v>2.823</v>
       </c>
       <c r="M93">
-        <v>8.300483929957769</v>
+        <v>8.391698039078184</v>
       </c>
       <c r="N93">
-        <v>-5.477483929957769</v>
+        <v>-5.568698039078184</v>
       </c>
       <c r="O93">
-        <v>-0.9037848484430319</v>
+        <v>-0.9188351764479004</v>
       </c>
       <c r="P93">
-        <v>-4.573699081514737</v>
+        <v>-4.649862862630283</v>
       </c>
       <c r="Q93">
-        <v>-4.422699081514737</v>
+        <v>-4.498862862630284</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4935843442912803</v>
+        <v>0.5495573873276904</v>
       </c>
       <c r="T93">
-        <v>8.728150330798789</v>
+        <v>9.81916912214864</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05611660764969036</v>
+        <v>0.05550664452306329</v>
       </c>
       <c r="W93">
-        <v>0.222567703916203</v>
+        <v>0.2227115332214617</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3401006524223659</v>
+        <v>0.3364039062003836</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.24885920154996</v>
+        <v>0.25075920154996</v>
       </c>
       <c r="C94">
-        <v>-23.84493228418672</v>
+        <v>-24.32493152938047</v>
       </c>
       <c r="D94">
-        <v>11.25426974752737</v>
+        <v>11.16109878528704</v>
       </c>
       <c r="E94">
-        <v>30.70537373637269</v>
+        <v>31.0922020193261</v>
       </c>
       <c r="F94">
-        <v>35.5882020317141</v>
+        <v>35.97503031466751</v>
       </c>
       <c r="G94">
         <v>0.489</v>
@@ -8977,37 +8977,37 @@
         <v>2.823</v>
       </c>
       <c r="M94">
-        <v>8.391698039078184</v>
+        <v>8.482912148198601</v>
       </c>
       <c r="N94">
-        <v>-5.568698039078184</v>
+        <v>-5.6599121481986</v>
       </c>
       <c r="O94">
-        <v>-0.9188351764479004</v>
+        <v>-0.9338855044527691</v>
       </c>
       <c r="P94">
-        <v>-4.649862862630283</v>
+        <v>-4.726026643745831</v>
       </c>
       <c r="Q94">
-        <v>-4.498862862630284</v>
+        <v>-4.575026643745831</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5495573873276904</v>
+        <v>0.6215227283745034</v>
       </c>
       <c r="T94">
-        <v>9.81916912214864</v>
+        <v>11.22190756816988</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05550664452306329</v>
+        <v>0.05490979888303035</v>
       </c>
       <c r="W94">
-        <v>0.2227115332214617</v>
+        <v>0.2228522694233814</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3364039062003836</v>
+        <v>0.3327866598971536</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.25075920154996</v>
+        <v>0.25265920154996</v>
       </c>
       <c r="C95">
-        <v>-24.32493152938047</v>
+        <v>-24.80340076821828</v>
       </c>
       <c r="D95">
-        <v>11.16109878528704</v>
+        <v>11.06945782940264</v>
       </c>
       <c r="E95">
-        <v>31.0922020193261</v>
+        <v>31.47903030227951</v>
       </c>
       <c r="F95">
-        <v>35.97503031466751</v>
+        <v>36.36185859762092</v>
       </c>
       <c r="G95">
         <v>0.489</v>
@@ -9059,37 +9059,37 @@
         <v>2.823</v>
       </c>
       <c r="M95">
-        <v>8.482912148198601</v>
+        <v>8.574126257319014</v>
       </c>
       <c r="N95">
-        <v>-5.6599121481986</v>
+        <v>-5.751126257319013</v>
       </c>
       <c r="O95">
-        <v>-0.9338855044527691</v>
+        <v>-0.9489358324576372</v>
       </c>
       <c r="P95">
-        <v>-4.726026643745831</v>
+        <v>-4.802190424861376</v>
       </c>
       <c r="Q95">
-        <v>-4.575026643745831</v>
+        <v>-4.651190424861376</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6215227283745034</v>
+        <v>0.7174765164369207</v>
       </c>
       <c r="T95">
-        <v>11.22190756816988</v>
+        <v>13.09222549619819</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05490979888303035</v>
+        <v>0.05432565208640237</v>
       </c>
       <c r="W95">
-        <v>0.2228522694233814</v>
+        <v>0.2229900112380263</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3327866598971536</v>
+        <v>0.3292463762812265</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.25265920154996</v>
+        <v>0.25455920154996</v>
       </c>
       <c r="C96">
-        <v>-24.80340076821828</v>
+        <v>-25.2803773812621</v>
       </c>
       <c r="D96">
-        <v>11.06945782940264</v>
+        <v>10.97930949931224</v>
       </c>
       <c r="E96">
-        <v>31.47903030227951</v>
+        <v>31.86585858523293</v>
       </c>
       <c r="F96">
-        <v>36.36185859762092</v>
+        <v>36.74868688057434</v>
       </c>
       <c r="G96">
         <v>0.489</v>
@@ -9141,37 +9141,37 @@
         <v>2.823</v>
       </c>
       <c r="M96">
-        <v>8.574126257319014</v>
+        <v>8.66534036643943</v>
       </c>
       <c r="N96">
-        <v>-5.751126257319013</v>
+        <v>-5.84234036643943</v>
       </c>
       <c r="O96">
-        <v>-0.9489358324576372</v>
+        <v>-0.963986160462506</v>
       </c>
       <c r="P96">
-        <v>-4.802190424861376</v>
+        <v>-4.878354205976924</v>
       </c>
       <c r="Q96">
-        <v>-4.651190424861376</v>
+        <v>-4.727354205976924</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7174765164369207</v>
+        <v>0.8518118197243053</v>
       </c>
       <c r="T96">
-        <v>13.09222549619819</v>
+        <v>15.71067059543784</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05432565208640237</v>
+        <v>0.05375380311707181</v>
       </c>
       <c r="W96">
-        <v>0.2229900112380263</v>
+        <v>0.2231248532249945</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3292463762812265</v>
+        <v>0.3257806249519504</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.25455920154996</v>
+        <v>0.25645920154996</v>
       </c>
       <c r="C97">
-        <v>-25.2803773812621</v>
+        <v>-25.75589754121932</v>
       </c>
       <c r="D97">
-        <v>10.97930949931224</v>
+        <v>10.89061762230843</v>
       </c>
       <c r="E97">
-        <v>31.86585858523293</v>
+        <v>32.25268686818634</v>
       </c>
       <c r="F97">
-        <v>36.74868688057434</v>
+        <v>37.13551516352776</v>
       </c>
       <c r="G97">
         <v>0.489</v>
@@ -9223,37 +9223,37 @@
         <v>2.823</v>
       </c>
       <c r="M97">
-        <v>8.66534036643943</v>
+        <v>8.756554475559845</v>
       </c>
       <c r="N97">
-        <v>-5.84234036643943</v>
+        <v>-5.933554475559845</v>
       </c>
       <c r="O97">
-        <v>-0.963986160462506</v>
+        <v>-0.9790364884673745</v>
       </c>
       <c r="P97">
-        <v>-4.878354205976924</v>
+        <v>-4.95451798709247</v>
       </c>
       <c r="Q97">
-        <v>-4.727354205976924</v>
+        <v>-4.80351798709247</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8518118197243053</v>
+        <v>1.053314774655382</v>
       </c>
       <c r="T97">
-        <v>15.71067059543784</v>
+        <v>19.63833824429731</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05375380311707181</v>
+        <v>0.05319386766793566</v>
       </c>
       <c r="W97">
-        <v>0.2231248532249945</v>
+        <v>0.2232568860039008</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3257806249519504</v>
+        <v>0.3223870767753676</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2564592015499599</v>
+        <v>0.2583592015499599</v>
       </c>
       <c r="C98">
-        <v>-25.75589754121931</v>
+        <v>-26.22999626133766</v>
       </c>
       <c r="D98">
-        <v>10.89061762230844</v>
+        <v>10.8033471851435</v>
       </c>
       <c r="E98">
-        <v>32.25268686818634</v>
+        <v>32.63951515113975</v>
       </c>
       <c r="F98">
-        <v>37.13551516352775</v>
+        <v>37.52234344648117</v>
       </c>
       <c r="G98">
         <v>0.489</v>
@@ -9305,37 +9305,37 @@
         <v>2.823</v>
       </c>
       <c r="M98">
-        <v>8.756554475559843</v>
+        <v>8.84776858468026</v>
       </c>
       <c r="N98">
-        <v>-5.933554475559843</v>
+        <v>-6.02476858468026</v>
       </c>
       <c r="O98">
-        <v>-0.9790364884673741</v>
+        <v>-0.9940868164722428</v>
       </c>
       <c r="P98">
-        <v>-4.954517987092469</v>
+        <v>-5.030681768208017</v>
       </c>
       <c r="Q98">
-        <v>-4.803517987092469</v>
+        <v>-4.879681768208017</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.053314774655379</v>
+        <v>1.389153032873839</v>
       </c>
       <c r="T98">
-        <v>19.63833824429725</v>
+        <v>26.18445099239634</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05319386766793566</v>
+        <v>0.05264547727960642</v>
       </c>
       <c r="W98">
-        <v>0.2232568860039008</v>
+        <v>0.2233861964574688</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3223870767753676</v>
+        <v>0.3190634986642813</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2583592015499599</v>
+        <v>0.26025920154996</v>
       </c>
       <c r="C99">
-        <v>-26.22999626133766</v>
+        <v>-26.70270744149174</v>
       </c>
       <c r="D99">
-        <v>10.8033471851435</v>
+        <v>10.71746428794284</v>
       </c>
       <c r="E99">
-        <v>32.63951515113975</v>
+        <v>33.02634343409317</v>
       </c>
       <c r="F99">
-        <v>37.52234344648117</v>
+        <v>37.90917172943458</v>
       </c>
       <c r="G99">
         <v>0.489</v>
@@ -9387,37 +9387,37 @@
         <v>2.823</v>
       </c>
       <c r="M99">
-        <v>8.84776858468026</v>
+        <v>8.938982693800675</v>
       </c>
       <c r="N99">
-        <v>-6.02476858468026</v>
+        <v>-6.115982693800674</v>
       </c>
       <c r="O99">
-        <v>-0.9940868164722428</v>
+        <v>-1.009137144477111</v>
       </c>
       <c r="P99">
-        <v>-5.030681768208017</v>
+        <v>-5.106845549323563</v>
       </c>
       <c r="Q99">
-        <v>-4.879681768208017</v>
+        <v>-4.955845549323564</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.389153032873839</v>
+        <v>2.060829549310759</v>
       </c>
       <c r="T99">
-        <v>26.18445099239634</v>
+        <v>39.2766764885945</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05264547727960642</v>
+        <v>0.05210827853185534</v>
       </c>
       <c r="W99">
-        <v>0.2233861964574688</v>
+        <v>0.2235128679221885</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3190634986642813</v>
+        <v>0.3158077486779111</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.26025920154996</v>
+        <v>0.26215920154996</v>
       </c>
       <c r="C100">
-        <v>-26.70270744149174</v>
+        <v>-27.17406391208861</v>
       </c>
       <c r="D100">
-        <v>10.71746428794284</v>
+        <v>10.63293610029939</v>
       </c>
       <c r="E100">
-        <v>33.02634343409317</v>
+        <v>33.41317171704658</v>
       </c>
       <c r="F100">
-        <v>37.90917172943458</v>
+        <v>38.29600001238799</v>
       </c>
       <c r="G100">
         <v>0.489</v>
@@ -9469,37 +9469,37 @@
         <v>2.823</v>
       </c>
       <c r="M100">
-        <v>8.938982693800675</v>
+        <v>9.03019680292109</v>
       </c>
       <c r="N100">
-        <v>-6.115982693800674</v>
+        <v>-6.207196802921089</v>
       </c>
       <c r="O100">
-        <v>-1.009137144477111</v>
+        <v>-1.02418747248198</v>
       </c>
       <c r="P100">
-        <v>-5.106845549323563</v>
+        <v>-5.183009330439109</v>
       </c>
       <c r="Q100">
-        <v>-4.955845549323564</v>
+        <v>-5.032009330439109</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.060829549310759</v>
+        <v>4.075859098621517</v>
       </c>
       <c r="T100">
-        <v>39.2766764885945</v>
+        <v>78.55335297718899</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05210827853185534</v>
+        <v>0.05158193228405882</v>
       </c>
       <c r="W100">
-        <v>0.2235128679221885</v>
+        <v>0.2236369803674189</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3158077486779111</v>
+        <v>0.3126177714185383</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.26215920154996</v>
-      </c>
-      <c r="C101">
-        <v>-27.17406391208861</v>
-      </c>
-      <c r="D101">
-        <v>10.63293610029939</v>
-      </c>
-      <c r="E101">
-        <v>33.41317171704658</v>
-      </c>
-      <c r="F101">
-        <v>38.29600001238799</v>
-      </c>
-      <c r="G101">
-        <v>0.489</v>
-      </c>
-      <c r="H101">
-        <v>33.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.974</v>
-      </c>
-      <c r="K101">
-        <v>0.151</v>
-      </c>
-      <c r="L101">
-        <v>2.823</v>
-      </c>
-      <c r="M101">
-        <v>9.03019680292109</v>
-      </c>
-      <c r="N101">
-        <v>-6.207196802921089</v>
-      </c>
-      <c r="O101">
-        <v>-1.02418747248198</v>
-      </c>
-      <c r="P101">
-        <v>-5.183009330439109</v>
-      </c>
-      <c r="Q101">
-        <v>-5.032009330439109</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.075859098621517</v>
-      </c>
-      <c r="T101">
-        <v>78.55335297718899</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05158193228405882</v>
-      </c>
-      <c r="W101">
-        <v>0.2236369803674189</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3126177714185383</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
